--- a/ms_teams_copilot_client_answers.xlsx
+++ b/ms_teams_copilot_client_answers.xlsx
@@ -8,27 +8,43 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohitVerma\Desktop\git\translation\SaS-to-python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F1D614-DC37-4B07-8043-A85FEA37EC31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB645F27-3797-4993-964A-D9DD09B5FAFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quick Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Answers" sheetId="2" r:id="rId2"/>
     <sheet name="Examples" sheetId="3" r:id="rId3"/>
     <sheet name="Scoring Metrics" sheetId="4" r:id="rId4"/>
+    <sheet name="Gemini trends" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId6"/>
+    <sheet name="Prompts" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Answers!$A$4:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Examples!$A$4:$F$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Quick Summary'!$A$4:$E$13</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="160">
   <si>
     <t>Quick summary for the client</t>
   </si>
@@ -453,12 +469,208 @@
   <si>
     <t>Apple Savings</t>
   </si>
+  <si>
+    <t>Barclays Online Saving</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Barclays Cards</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Synchrony Online Saving</t>
+  </si>
+  <si>
+    <t>Synchrony Cards</t>
+  </si>
+  <si>
+    <t>American Express Online Saving</t>
+  </si>
+  <si>
+    <t>American Express Cards</t>
+  </si>
+  <si>
+    <t>Capital One Online Saving</t>
+  </si>
+  <si>
+    <t>Capital One Cards</t>
+  </si>
+  <si>
+    <t>SoFi Online Saving</t>
+  </si>
+  <si>
+    <t>SoFi Cards</t>
+  </si>
+  <si>
+    <t>Ally Online Saving</t>
+  </si>
+  <si>
+    <t>Ally Cards</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Estimated_Search_Volume</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>November</t>
+  </si>
+  <si>
+    <t>December</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visit the following page 
+https://www.nerdwallet.com/m/banking/standout-online-savings-accounts-2
+scrap all the content which is available on the page.
+extract the data under heading ```Standout Online Savings Accounts``` 
+provide the data in a tabular format 
+Rank (1, 2, 3, …)
+Bank/Institution name (short name)
+Product name (full name with bank)
+APY (annual percentage yield) (x.xx%)
+rating
+Bonus: if any (empty if not available)
+Notes: (minimum balance, eligibility, account type, restrictions — if not stated, empty)
+</t>
+  </si>
+  <si>
+    <t>fetch competitor APY data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visit the following page 
+https://www.nerdwallet.com/best/banking/high-yield-online-savings-accounts 
+scrap all the content which is available on the page.
+extract the data under heading ```Best High-Yield Savings Accounts of October 2025: ```
+provide the data in a tabular format 
+Rank (1, 2, 3, …)
+Bank/Institution name (short name)
+Product name (full name with bank)
+APY (annual percentage yield)
+rating
+Bonus: if any (empty if not available)
+Notes: (minimum balance, eligibility, account type, restrictions — if not stated, empty)
+</t>
+  </si>
+  <si>
+    <t>Visit each of the following links and extract the complete, ordered list of banks or financial institutions and their savings-account offers.
+Links:
+https://www.nerdwallet.com/best/banking/savings-accounts
+https://www.bankrate.com/banking/savings/rates/
+https://www.bestmoney.com/online-banking/compare-savings-accounts
+Special instruction for Bankrate:
+Only extract banks listed under the section “Best high-yield savings accounts for {current month + year}.”
+For each offer, return one row with the following columns:
+Publisher (NerdWallet / Bankrate / BestMoney)
+Rank Order (keep the exact order shown on the page)
+Bank – the bank or institution name only
+Product – the full account name (e.g., Openbank High Yield Savings)
+APY (format as x.xx %)
+Publisher Rating
+Bonus (if available; otherwise null)
+Notes (minimum balance, eligibility, account type, restrictions — if not stated, null)
+Formatting rules:
+Do not include hyperlinks.
+Keep the original on-page order exactly.
+Record missing fields as null.
+Normalize APY strictly to the format x.xx%.
+Include both “Bank” and “Product” columns (e.g.,
+Bank = Openbank, Product = Openbank High Yield Savings).
+Output:
+Combine all extracted rows from all three publishers into a single Excel file named
+savings_offers_with_bank.xlsx, with columns ordered as:
+Publisher | Rank Order | Bank | Product | APY | Publisher Rating | Bonus | Notes.</t>
+  </si>
+  <si>
+    <t>Barclays sentiments</t>
+  </si>
+  <si>
+    <t>Analyze the 2025 Doctor of Credit comments on “Barclays Savings”. Extract the top five positive and top five negative comment themes. Represent each as a hashtag with a short label and an approximate count of occurrences. Present the results in a clean two-section table — one for positives and one for negatives.</t>
+  </si>
+  <si>
+    <t>top 5 saving products in 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I want you to run the comparative analysis
+do the following
+visit **Doctor of Credit** and **reddit** for 
+most discussed savings products** within the **U.S. banking market** for the 2025.
+combine the data from both of the sources.
+Extract and rank the **top 5 savings or deposit products** (e.g., Barclays Saving, SoFi, Ally, Capital One, Marcus, AmEx, etc.) by **discussion volume**. 
+3. Provide the aggregate number of comments/topics/discussions of each product from the combined data.
+4. Present results in a **table** with the following columns:
+   - Rank  
+   - Product / Provider Name  
+   - Approx. Discussion Share or Mentions  (number and  percentage)
+   - Common Themes (e.g., customer service, APY, account freezes)   
+   - Representative Thread or Quote (with link if available)
+ Summarize insights in 1–2 paragraphs highlighting what drives discussion volume (e.g., promotions, rate cuts, scandals, or UX).
+Return the final output as a **Markdown table**. 
+</t>
+  </si>
+  <si>
+    <t>top 5 monthly saving products in 2025</t>
+  </si>
+  <si>
+    <t>I want you to run the comparative analysis_x000D_
+_x000D_
+do the following_x000D_
+visit **Doctor of Credit** and **reddit** for _x000D_
+most discussed savings products** within the **U.S. banking market** for the January 2025._x000D_
+combine the data from both of the sources._x000D_
+Extract and rank the **top 5 savings or deposit products** (e.g., Barclays Saving, SoFi, Ally, Capital One, Marcus, AmEx, etc.) by **discussion volume**. _x000D_
+3. Provide the aggregate number of comments/topics/discussions of each product from the combined data._x000D_
+4. Present results in a **table** with the following columns:_x000D_
+   - Rank  _x000D_
+   - Product / Provider Name  _x000D_
+   - Approx. Discussion Share or Mentions  (number and  percentage)_x000D_
+   - Common Themes (e.g., customer service, APY, account freezes)   _x000D_
+   - Representative Thread or Quote (with link if available)_x000D_
+_x000D_
+ Summarize insights in 1–2 paragraphs highlighting what drives discussion volume (e.g., promotions, rate cuts, scandals, or UX)._x000D_
+_x000D_
+Return the final output as a **Markdown table**. _x000D_</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -507,8 +719,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -550,6 +768,12 @@
         <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -587,7 +811,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -618,6 +842,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="15" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -628,6 +859,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -643,6 +875,1233 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Estimated_Search_Volume</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$F$2:$F$62</c:f>
+              <c:strCache>
+                <c:ptCount val="61"/>
+                <c:pt idx="0">
+                  <c:v>2021 April</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2021 May</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2021 June</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2021 July</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2021 August</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2021 September</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2021 October</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2021 November</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2021 December</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2022 January</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2022 February</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2022 March</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2022 April</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2022 May</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2022 June</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2022 July</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2022 August</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2022 September</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2022 October</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2022 November</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2022 December</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2023 January</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2023 February</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023 March</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2023 April</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2023 May</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2023 June</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2023 July</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2023 August</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2023 September</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2023 October</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2023 November</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2023 December</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2024 January</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2024 February</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2024 March</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2024 April</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2024 May</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2024 June</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2024 July</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2024 August</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2024 September</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2024 October</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2024 November</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2024 December</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2025 January</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2025 February</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2025 March</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2025 April</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2025 May</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2025 June</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2025 July</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2025 August</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2025 September</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2025 October</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2025 November</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2025 December</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2026 January</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2026 February</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2026 March</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2026 April</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$G$2:$G$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="61"/>
+                <c:pt idx="0">
+                  <c:v>135000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>140000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>138000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>145000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>150000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>148000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>155000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>160000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>158000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>180000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>175000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>190000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>201000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>210000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>225000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>240000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>255000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>270000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>300000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>310000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>290000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>330000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>315000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>350000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>340000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>330000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>320000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>345000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>360000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>355000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>370000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>365000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>350000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>390000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>380000</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>400000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>395000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>385000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>375000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>390000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>410000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>405000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>420000</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>415000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>400000</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>440000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>430000</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>455000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>450000</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>440000</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>435000</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>450000</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>470000</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>465000</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>480000</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>475000</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>460000</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>500000</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>490000</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>510000</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>505000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0442-4913-AB23-D24E16F3E970}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="605817071"/>
+        <c:axId val="605842511"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="605817071"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="605842511"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="605842511"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="605817071"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>307975</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>3175</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B93CA25C-C679-F130-6FCE-B06700032A0F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -941,22 +2400,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
     </row>
     <row r="4" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -1154,40 +2613,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -1473,24 +2932,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="4" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -1974,4 +3433,2552 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34410FB3-3D8B-4DC0-8456-5DE07D37318C}">
+  <dimension ref="A1:R69"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.90625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K1" t="s">
+        <v>132</v>
+      </c>
+      <c r="L1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N1" t="s">
+        <v>130</v>
+      </c>
+      <c r="O1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>128</v>
+      </c>
+      <c r="R1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A2" s="13">
+        <v>44347</v>
+      </c>
+      <c r="B2">
+        <v>10800</v>
+      </c>
+      <c r="C2">
+        <v>22200</v>
+      </c>
+      <c r="E2">
+        <v>27100</v>
+      </c>
+      <c r="F2">
+        <v>2810</v>
+      </c>
+      <c r="H2">
+        <v>33100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A3" s="13">
+        <v>44377</v>
+      </c>
+      <c r="B3">
+        <v>11200</v>
+      </c>
+      <c r="C3">
+        <v>24600</v>
+      </c>
+      <c r="E3">
+        <v>22200</v>
+      </c>
+      <c r="F3">
+        <v>2950</v>
+      </c>
+      <c r="G3" s="12"/>
+      <c r="H3">
+        <v>31200</v>
+      </c>
+      <c r="J3" s="13"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A4" s="13">
+        <v>44408</v>
+      </c>
+      <c r="B4">
+        <v>11400</v>
+      </c>
+      <c r="C4">
+        <v>22200</v>
+      </c>
+      <c r="D4" s="12"/>
+      <c r="E4">
+        <v>18100</v>
+      </c>
+      <c r="F4">
+        <v>3100</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4">
+        <v>32500</v>
+      </c>
+      <c r="J4" s="13"/>
+      <c r="M4" s="13"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A5" s="13">
+        <v>44439</v>
+      </c>
+      <c r="B5">
+        <v>10900</v>
+      </c>
+      <c r="C5">
+        <v>18100</v>
+      </c>
+      <c r="D5" s="14"/>
+      <c r="E5">
+        <v>20100</v>
+      </c>
+      <c r="F5">
+        <v>3320</v>
+      </c>
+      <c r="G5" s="14"/>
+      <c r="H5">
+        <v>30800</v>
+      </c>
+      <c r="J5" s="13"/>
+      <c r="M5" s="13"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A6" s="13">
+        <v>44469</v>
+      </c>
+      <c r="B6">
+        <v>10700</v>
+      </c>
+      <c r="C6">
+        <v>22200</v>
+      </c>
+      <c r="D6" s="14"/>
+      <c r="E6">
+        <v>18100</v>
+      </c>
+      <c r="F6">
+        <v>3080</v>
+      </c>
+      <c r="G6" s="14"/>
+      <c r="H6">
+        <v>29400</v>
+      </c>
+      <c r="J6" s="13"/>
+      <c r="M6" s="13"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A7" s="13">
+        <v>44500</v>
+      </c>
+      <c r="B7">
+        <v>11100</v>
+      </c>
+      <c r="C7">
+        <v>18100</v>
+      </c>
+      <c r="D7" s="14"/>
+      <c r="E7">
+        <v>14800</v>
+      </c>
+      <c r="F7">
+        <v>4200</v>
+      </c>
+      <c r="G7" s="14"/>
+      <c r="H7">
+        <v>28700</v>
+      </c>
+      <c r="J7" s="13"/>
+      <c r="M7" s="13"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A8" s="13">
+        <v>44530</v>
+      </c>
+      <c r="B8">
+        <v>11500</v>
+      </c>
+      <c r="C8">
+        <v>14800</v>
+      </c>
+      <c r="D8" s="14"/>
+      <c r="E8">
+        <v>14800</v>
+      </c>
+      <c r="F8">
+        <v>4150</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8">
+        <v>30100</v>
+      </c>
+      <c r="J8" s="13"/>
+      <c r="M8" s="13"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A9" s="13">
+        <v>44561</v>
+      </c>
+      <c r="B9">
+        <v>12200</v>
+      </c>
+      <c r="C9">
+        <v>18100</v>
+      </c>
+      <c r="D9" s="14"/>
+      <c r="E9">
+        <v>14800</v>
+      </c>
+      <c r="F9">
+        <v>4670</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9">
+        <v>31600</v>
+      </c>
+      <c r="J9" s="13"/>
+      <c r="M9" s="13"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A10" s="13">
+        <v>44592</v>
+      </c>
+      <c r="B10">
+        <v>14800</v>
+      </c>
+      <c r="C10">
+        <v>18100</v>
+      </c>
+      <c r="D10" s="14"/>
+      <c r="E10">
+        <v>14800</v>
+      </c>
+      <c r="F10">
+        <v>5100</v>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="H10">
+        <v>34200</v>
+      </c>
+      <c r="J10" s="13"/>
+      <c r="M10" s="13"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A11" s="13">
+        <v>44620</v>
+      </c>
+      <c r="B11">
+        <v>13900</v>
+      </c>
+      <c r="C11">
+        <v>14800</v>
+      </c>
+      <c r="D11" s="14"/>
+      <c r="E11">
+        <v>18100</v>
+      </c>
+      <c r="F11">
+        <v>4890</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11">
+        <v>31800</v>
+      </c>
+      <c r="J11" s="13"/>
+      <c r="M11" s="13"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A12" s="13">
+        <v>44651</v>
+      </c>
+      <c r="B12">
+        <v>14500</v>
+      </c>
+      <c r="C12">
+        <v>18100</v>
+      </c>
+      <c r="D12" s="14"/>
+      <c r="E12">
+        <v>18100</v>
+      </c>
+      <c r="F12">
+        <v>5230</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12">
+        <v>33500</v>
+      </c>
+      <c r="J12" s="13"/>
+      <c r="M12" s="13"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A13" s="13">
+        <v>44681</v>
+      </c>
+      <c r="B13">
+        <v>15200</v>
+      </c>
+      <c r="C13">
+        <v>18100</v>
+      </c>
+      <c r="D13" s="14"/>
+      <c r="E13">
+        <v>22200</v>
+      </c>
+      <c r="F13">
+        <v>5410</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13">
+        <v>32100</v>
+      </c>
+      <c r="J13" s="13"/>
+      <c r="M13" s="13"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A14" s="13">
+        <v>44712</v>
+      </c>
+      <c r="B14">
+        <v>16100</v>
+      </c>
+      <c r="C14">
+        <v>14800</v>
+      </c>
+      <c r="D14" s="14"/>
+      <c r="E14">
+        <v>22200</v>
+      </c>
+      <c r="F14">
+        <v>5600</v>
+      </c>
+      <c r="G14" s="14"/>
+      <c r="H14">
+        <v>34400</v>
+      </c>
+      <c r="J14" s="13"/>
+      <c r="M14" s="13"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A15" s="13">
+        <v>44742</v>
+      </c>
+      <c r="B15">
+        <v>17800</v>
+      </c>
+      <c r="C15">
+        <v>18100</v>
+      </c>
+      <c r="D15" s="14"/>
+      <c r="E15">
+        <v>22200</v>
+      </c>
+      <c r="F15">
+        <v>5820</v>
+      </c>
+      <c r="G15" s="14"/>
+      <c r="H15">
+        <v>36800</v>
+      </c>
+      <c r="J15" s="13"/>
+      <c r="M15" s="13"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A16" s="13">
+        <v>44773</v>
+      </c>
+      <c r="B16">
+        <v>18900</v>
+      </c>
+      <c r="C16">
+        <v>18100</v>
+      </c>
+      <c r="D16" s="14"/>
+      <c r="E16">
+        <v>27100</v>
+      </c>
+      <c r="F16">
+        <v>6100</v>
+      </c>
+      <c r="G16" s="14"/>
+      <c r="H16">
+        <v>38100</v>
+      </c>
+      <c r="J16" s="13"/>
+      <c r="M16" s="13"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" s="13">
+        <v>44804</v>
+      </c>
+      <c r="B17">
+        <v>19500</v>
+      </c>
+      <c r="C17">
+        <v>22200</v>
+      </c>
+      <c r="D17" s="14"/>
+      <c r="E17">
+        <v>27100</v>
+      </c>
+      <c r="F17">
+        <v>6350</v>
+      </c>
+      <c r="G17" s="14"/>
+      <c r="H17">
+        <v>39500</v>
+      </c>
+      <c r="J17" s="13"/>
+      <c r="M17" s="13"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" s="13">
+        <v>44834</v>
+      </c>
+      <c r="B18">
+        <v>21200</v>
+      </c>
+      <c r="C18">
+        <v>18100</v>
+      </c>
+      <c r="D18" s="14"/>
+      <c r="E18">
+        <v>27100</v>
+      </c>
+      <c r="F18">
+        <v>6210</v>
+      </c>
+      <c r="G18" s="14"/>
+      <c r="H18">
+        <v>41200</v>
+      </c>
+      <c r="J18" s="13"/>
+      <c r="M18" s="13"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" s="13">
+        <v>44865</v>
+      </c>
+      <c r="B19">
+        <v>24500</v>
+      </c>
+      <c r="C19">
+        <v>18100</v>
+      </c>
+      <c r="D19" s="14"/>
+      <c r="E19">
+        <v>33100</v>
+      </c>
+      <c r="F19">
+        <v>6480</v>
+      </c>
+      <c r="G19" s="14"/>
+      <c r="H19">
+        <v>42700</v>
+      </c>
+      <c r="J19" s="13"/>
+      <c r="M19" s="13"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20" s="13">
+        <v>44895</v>
+      </c>
+      <c r="B20">
+        <v>25800</v>
+      </c>
+      <c r="C20">
+        <v>14800</v>
+      </c>
+      <c r="D20" s="14"/>
+      <c r="E20">
+        <v>40500</v>
+      </c>
+      <c r="F20">
+        <v>6700</v>
+      </c>
+      <c r="G20" s="14"/>
+      <c r="H20">
+        <v>44100</v>
+      </c>
+      <c r="J20" s="13"/>
+      <c r="M20" s="13"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21" s="13">
+        <v>44926</v>
+      </c>
+      <c r="B21">
+        <v>26900</v>
+      </c>
+      <c r="C21">
+        <v>14800</v>
+      </c>
+      <c r="D21" s="14"/>
+      <c r="E21">
+        <v>40500</v>
+      </c>
+      <c r="F21">
+        <v>6920</v>
+      </c>
+      <c r="G21" s="14"/>
+      <c r="H21">
+        <v>43200</v>
+      </c>
+      <c r="J21" s="13"/>
+      <c r="M21" s="13"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22" s="13">
+        <v>44957</v>
+      </c>
+      <c r="B22">
+        <v>31200</v>
+      </c>
+      <c r="C22">
+        <v>18100</v>
+      </c>
+      <c r="D22" s="14"/>
+      <c r="E22">
+        <v>40500</v>
+      </c>
+      <c r="F22">
+        <v>7450</v>
+      </c>
+      <c r="G22" s="14"/>
+      <c r="H22">
+        <v>46500</v>
+      </c>
+      <c r="J22" s="13"/>
+      <c r="M22" s="13"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" s="13">
+        <v>44985</v>
+      </c>
+      <c r="B23">
+        <v>33500</v>
+      </c>
+      <c r="C23">
+        <v>14800</v>
+      </c>
+      <c r="D23" s="14"/>
+      <c r="E23">
+        <v>49500</v>
+      </c>
+      <c r="F23">
+        <v>7120</v>
+      </c>
+      <c r="G23" s="14"/>
+      <c r="H23">
+        <v>45100</v>
+      </c>
+      <c r="J23" s="13"/>
+      <c r="M23" s="13"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24" s="13">
+        <v>45016</v>
+      </c>
+      <c r="B24">
+        <v>44200</v>
+      </c>
+      <c r="C24">
+        <v>18100</v>
+      </c>
+      <c r="D24" s="14"/>
+      <c r="E24">
+        <v>49500</v>
+      </c>
+      <c r="F24">
+        <v>7800</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24">
+        <v>49800</v>
+      </c>
+      <c r="J24" s="13"/>
+      <c r="M24" s="13"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A25" s="13">
+        <v>45046</v>
+      </c>
+      <c r="B25">
+        <v>42800</v>
+      </c>
+      <c r="C25">
+        <v>18100</v>
+      </c>
+      <c r="D25" s="14"/>
+      <c r="E25">
+        <v>60500</v>
+      </c>
+      <c r="F25">
+        <v>8100</v>
+      </c>
+      <c r="G25" s="14"/>
+      <c r="H25">
+        <v>48200</v>
+      </c>
+      <c r="J25" s="13"/>
+      <c r="M25" s="13"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A26" s="13">
+        <v>45077</v>
+      </c>
+      <c r="B26">
+        <v>41500</v>
+      </c>
+      <c r="C26">
+        <v>18100</v>
+      </c>
+      <c r="D26" s="14"/>
+      <c r="E26">
+        <v>49500</v>
+      </c>
+      <c r="F26">
+        <v>8350</v>
+      </c>
+      <c r="G26" s="14"/>
+      <c r="H26">
+        <v>47900</v>
+      </c>
+      <c r="J26" s="13"/>
+      <c r="M26" s="13"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A27" s="13">
+        <v>45107</v>
+      </c>
+      <c r="B27">
+        <v>40100</v>
+      </c>
+      <c r="C27">
+        <v>22200</v>
+      </c>
+      <c r="D27" s="14"/>
+      <c r="E27">
+        <v>49500</v>
+      </c>
+      <c r="F27">
+        <v>8600</v>
+      </c>
+      <c r="G27" s="14"/>
+      <c r="H27">
+        <v>49100</v>
+      </c>
+      <c r="J27" s="13"/>
+      <c r="M27" s="13"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A28" s="13">
+        <v>45138</v>
+      </c>
+      <c r="B28">
+        <v>41200</v>
+      </c>
+      <c r="C28">
+        <v>22200</v>
+      </c>
+      <c r="D28" s="14"/>
+      <c r="E28">
+        <v>60500</v>
+      </c>
+      <c r="F28">
+        <v>8920</v>
+      </c>
+      <c r="G28" s="14"/>
+      <c r="H28">
+        <v>50300</v>
+      </c>
+      <c r="J28" s="13"/>
+      <c r="M28" s="13"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A29" s="13">
+        <v>45169</v>
+      </c>
+      <c r="B29">
+        <v>40800</v>
+      </c>
+      <c r="C29">
+        <v>22200</v>
+      </c>
+      <c r="D29" s="14"/>
+      <c r="E29">
+        <v>60500</v>
+      </c>
+      <c r="F29">
+        <v>9150</v>
+      </c>
+      <c r="G29" s="14"/>
+      <c r="H29">
+        <v>51400</v>
+      </c>
+      <c r="J29" s="13"/>
+      <c r="M29" s="13"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A30" s="13">
+        <v>45199</v>
+      </c>
+      <c r="B30">
+        <v>39500</v>
+      </c>
+      <c r="C30">
+        <v>18100</v>
+      </c>
+      <c r="D30" s="14"/>
+      <c r="E30">
+        <v>60500</v>
+      </c>
+      <c r="F30">
+        <v>8800</v>
+      </c>
+      <c r="G30" s="14"/>
+      <c r="H30">
+        <v>50800</v>
+      </c>
+      <c r="J30" s="13"/>
+      <c r="M30" s="13"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A31" s="13">
+        <v>45230</v>
+      </c>
+      <c r="B31">
+        <v>42100</v>
+      </c>
+      <c r="C31">
+        <v>18100</v>
+      </c>
+      <c r="D31" s="14"/>
+      <c r="E31">
+        <v>49500</v>
+      </c>
+      <c r="F31">
+        <v>9240</v>
+      </c>
+      <c r="G31" s="14"/>
+      <c r="H31">
+        <v>49600</v>
+      </c>
+      <c r="J31" s="13"/>
+      <c r="M31" s="13"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A32" s="13">
+        <v>45260</v>
+      </c>
+      <c r="B32">
+        <v>40600</v>
+      </c>
+      <c r="C32">
+        <v>18100</v>
+      </c>
+      <c r="D32" s="14"/>
+      <c r="E32">
+        <v>49500</v>
+      </c>
+      <c r="F32">
+        <v>9510</v>
+      </c>
+      <c r="G32" s="14"/>
+      <c r="H32">
+        <v>48700</v>
+      </c>
+      <c r="J32" s="13"/>
+      <c r="M32" s="13"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A33" s="13">
+        <v>45291</v>
+      </c>
+      <c r="B33">
+        <v>38900</v>
+      </c>
+      <c r="C33">
+        <v>14800</v>
+      </c>
+      <c r="D33" s="14"/>
+      <c r="E33">
+        <v>40500</v>
+      </c>
+      <c r="F33">
+        <v>9800</v>
+      </c>
+      <c r="G33" s="14"/>
+      <c r="H33">
+        <v>49200</v>
+      </c>
+      <c r="J33" s="13"/>
+      <c r="M33" s="13"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A34" s="13">
+        <v>45322</v>
+      </c>
+      <c r="B34">
+        <v>43500</v>
+      </c>
+      <c r="C34">
+        <v>18100</v>
+      </c>
+      <c r="D34" s="14"/>
+      <c r="E34">
+        <v>40500</v>
+      </c>
+      <c r="F34">
+        <v>10200</v>
+      </c>
+      <c r="G34" s="14"/>
+      <c r="H34">
+        <v>52100</v>
+      </c>
+      <c r="J34" s="13"/>
+      <c r="M34" s="13"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A35" s="13">
+        <v>45351</v>
+      </c>
+      <c r="B35">
+        <v>41200</v>
+      </c>
+      <c r="C35">
+        <v>18100</v>
+      </c>
+      <c r="D35" s="14"/>
+      <c r="E35">
+        <v>49500</v>
+      </c>
+      <c r="F35">
+        <v>9950</v>
+      </c>
+      <c r="G35" s="14"/>
+      <c r="H35">
+        <v>50400</v>
+      </c>
+      <c r="J35" s="13"/>
+      <c r="M35" s="13"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A36" s="13">
+        <v>45382</v>
+      </c>
+      <c r="B36">
+        <v>39800</v>
+      </c>
+      <c r="C36">
+        <v>22200</v>
+      </c>
+      <c r="D36" s="14"/>
+      <c r="E36">
+        <v>40500</v>
+      </c>
+      <c r="F36">
+        <v>10600</v>
+      </c>
+      <c r="G36" s="14"/>
+      <c r="H36">
+        <v>51700</v>
+      </c>
+      <c r="J36" s="13"/>
+      <c r="M36" s="13"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A37" s="13">
+        <v>45412</v>
+      </c>
+      <c r="B37">
+        <v>38200</v>
+      </c>
+      <c r="C37">
+        <v>22200</v>
+      </c>
+      <c r="D37" s="14"/>
+      <c r="E37">
+        <v>40500</v>
+      </c>
+      <c r="F37">
+        <v>10900</v>
+      </c>
+      <c r="G37" s="14"/>
+      <c r="H37">
+        <v>50900</v>
+      </c>
+      <c r="J37" s="13"/>
+      <c r="M37" s="13"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A38" s="13">
+        <v>45443</v>
+      </c>
+      <c r="B38">
+        <v>37500</v>
+      </c>
+      <c r="C38">
+        <v>22200</v>
+      </c>
+      <c r="D38" s="14"/>
+      <c r="E38">
+        <v>33100</v>
+      </c>
+      <c r="F38">
+        <v>11200</v>
+      </c>
+      <c r="G38" s="14"/>
+      <c r="H38">
+        <v>49800</v>
+      </c>
+      <c r="J38" s="13"/>
+      <c r="M38" s="13"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A39" s="13">
+        <v>45473</v>
+      </c>
+      <c r="B39">
+        <v>36900</v>
+      </c>
+      <c r="C39">
+        <v>27100</v>
+      </c>
+      <c r="D39" s="14"/>
+      <c r="E39">
+        <v>33100</v>
+      </c>
+      <c r="F39">
+        <v>11550</v>
+      </c>
+      <c r="G39" s="14"/>
+      <c r="H39">
+        <v>48500</v>
+      </c>
+      <c r="J39" s="13"/>
+      <c r="M39" s="13"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A40" s="13">
+        <v>45504</v>
+      </c>
+      <c r="B40">
+        <v>37400</v>
+      </c>
+      <c r="C40">
+        <v>27100</v>
+      </c>
+      <c r="D40" s="14"/>
+      <c r="E40">
+        <v>33100</v>
+      </c>
+      <c r="F40">
+        <v>12100</v>
+      </c>
+      <c r="G40" s="14"/>
+      <c r="H40">
+        <v>50100</v>
+      </c>
+      <c r="J40" s="13"/>
+      <c r="M40" s="13"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A41" s="13">
+        <v>45535</v>
+      </c>
+      <c r="B41">
+        <v>38100</v>
+      </c>
+      <c r="C41">
+        <v>22200</v>
+      </c>
+      <c r="D41" s="14"/>
+      <c r="E41">
+        <v>33100</v>
+      </c>
+      <c r="F41">
+        <v>12400</v>
+      </c>
+      <c r="G41" s="14"/>
+      <c r="H41">
+        <v>49200</v>
+      </c>
+      <c r="J41" s="13"/>
+      <c r="M41" s="13"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A42" s="13">
+        <v>45565</v>
+      </c>
+      <c r="B42">
+        <v>39200</v>
+      </c>
+      <c r="C42">
+        <v>22200</v>
+      </c>
+      <c r="D42" s="14"/>
+      <c r="E42">
+        <v>27100</v>
+      </c>
+      <c r="F42">
+        <v>11950</v>
+      </c>
+      <c r="G42" s="14"/>
+      <c r="H42">
+        <v>47800</v>
+      </c>
+      <c r="J42" s="13"/>
+      <c r="M42" s="13"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A43" s="13">
+        <v>45596</v>
+      </c>
+      <c r="B43">
+        <v>38800</v>
+      </c>
+      <c r="C43">
+        <v>22200</v>
+      </c>
+      <c r="D43" s="14"/>
+      <c r="E43">
+        <v>27100</v>
+      </c>
+      <c r="F43">
+        <v>12300</v>
+      </c>
+      <c r="G43" s="14"/>
+      <c r="H43">
+        <v>48300</v>
+      </c>
+      <c r="J43" s="13"/>
+      <c r="M43" s="13"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A44" s="13">
+        <v>45626</v>
+      </c>
+      <c r="B44">
+        <v>37500</v>
+      </c>
+      <c r="C44">
+        <v>18100</v>
+      </c>
+      <c r="D44" s="14"/>
+      <c r="E44">
+        <v>22200</v>
+      </c>
+      <c r="F44">
+        <v>12750</v>
+      </c>
+      <c r="G44" s="14"/>
+      <c r="H44">
+        <v>47100</v>
+      </c>
+      <c r="J44" s="13"/>
+      <c r="M44" s="13"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A45" s="13">
+        <v>45657</v>
+      </c>
+      <c r="B45">
+        <v>36200</v>
+      </c>
+      <c r="C45">
+        <v>18100</v>
+      </c>
+      <c r="D45" s="14"/>
+      <c r="E45">
+        <v>22200</v>
+      </c>
+      <c r="F45">
+        <v>13100</v>
+      </c>
+      <c r="G45" s="14"/>
+      <c r="H45">
+        <v>47900</v>
+      </c>
+      <c r="J45" s="13"/>
+      <c r="M45" s="13"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A46" s="13">
+        <v>45688</v>
+      </c>
+      <c r="B46">
+        <v>39500</v>
+      </c>
+      <c r="C46">
+        <v>22200</v>
+      </c>
+      <c r="D46" s="14"/>
+      <c r="E46">
+        <v>18100</v>
+      </c>
+      <c r="F46">
+        <v>13800</v>
+      </c>
+      <c r="G46" s="14"/>
+      <c r="H46">
+        <v>50600</v>
+      </c>
+      <c r="J46" s="13"/>
+      <c r="M46" s="13"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A47" s="13">
+        <v>45716</v>
+      </c>
+      <c r="B47">
+        <v>37200</v>
+      </c>
+      <c r="C47">
+        <v>18100</v>
+      </c>
+      <c r="D47" s="14"/>
+      <c r="E47">
+        <v>22200</v>
+      </c>
+      <c r="F47">
+        <v>13450</v>
+      </c>
+      <c r="G47" s="14"/>
+      <c r="H47">
+        <v>49200</v>
+      </c>
+      <c r="J47" s="13"/>
+      <c r="M47" s="13"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A48" s="13">
+        <v>45747</v>
+      </c>
+      <c r="B48">
+        <v>36800</v>
+      </c>
+      <c r="C48">
+        <v>22200</v>
+      </c>
+      <c r="D48" s="14"/>
+      <c r="E48">
+        <v>22200</v>
+      </c>
+      <c r="F48">
+        <v>14200</v>
+      </c>
+      <c r="G48" s="14"/>
+      <c r="H48">
+        <v>51300</v>
+      </c>
+      <c r="J48" s="13"/>
+      <c r="M48" s="13"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A49" s="13">
+        <v>45777</v>
+      </c>
+      <c r="B49">
+        <v>35500</v>
+      </c>
+      <c r="C49">
+        <v>22200</v>
+      </c>
+      <c r="D49" s="14"/>
+      <c r="E49">
+        <v>22200</v>
+      </c>
+      <c r="F49">
+        <v>14600</v>
+      </c>
+      <c r="G49" s="14"/>
+      <c r="H49">
+        <v>50100</v>
+      </c>
+      <c r="J49" s="13"/>
+      <c r="M49" s="13"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A50" s="13">
+        <v>45808</v>
+      </c>
+      <c r="B50">
+        <v>34200</v>
+      </c>
+      <c r="C50">
+        <v>27100</v>
+      </c>
+      <c r="D50" s="14"/>
+      <c r="E50">
+        <v>18100</v>
+      </c>
+      <c r="F50">
+        <v>14900</v>
+      </c>
+      <c r="G50" s="14"/>
+      <c r="H50">
+        <v>49400</v>
+      </c>
+      <c r="J50" s="13"/>
+      <c r="M50" s="13"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A51" s="13">
+        <v>45838</v>
+      </c>
+      <c r="B51">
+        <v>33100</v>
+      </c>
+      <c r="C51">
+        <v>27100</v>
+      </c>
+      <c r="D51" s="14"/>
+      <c r="E51">
+        <v>18100</v>
+      </c>
+      <c r="F51">
+        <v>15300</v>
+      </c>
+      <c r="G51" s="14"/>
+      <c r="H51">
+        <v>48200</v>
+      </c>
+      <c r="J51" s="13"/>
+      <c r="M51" s="13"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A52" s="13">
+        <v>45869</v>
+      </c>
+      <c r="B52">
+        <v>33800</v>
+      </c>
+      <c r="C52">
+        <v>33100</v>
+      </c>
+      <c r="D52" s="14"/>
+      <c r="E52">
+        <v>18100</v>
+      </c>
+      <c r="F52">
+        <v>15800</v>
+      </c>
+      <c r="G52" s="14"/>
+      <c r="H52">
+        <v>49700</v>
+      </c>
+      <c r="J52" s="13"/>
+      <c r="M52" s="13"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A53" s="13">
+        <v>45900</v>
+      </c>
+      <c r="B53">
+        <v>34500</v>
+      </c>
+      <c r="C53">
+        <v>27100</v>
+      </c>
+      <c r="D53" s="14"/>
+      <c r="E53">
+        <v>18100</v>
+      </c>
+      <c r="F53">
+        <v>16200</v>
+      </c>
+      <c r="G53" s="14"/>
+      <c r="H53">
+        <v>48800</v>
+      </c>
+      <c r="J53" s="13"/>
+      <c r="M53" s="13"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A54" s="13">
+        <v>45930</v>
+      </c>
+      <c r="B54">
+        <v>32900</v>
+      </c>
+      <c r="C54">
+        <v>27100</v>
+      </c>
+      <c r="D54" s="14"/>
+      <c r="E54">
+        <v>14800</v>
+      </c>
+      <c r="F54">
+        <v>15700</v>
+      </c>
+      <c r="G54" s="14"/>
+      <c r="H54">
+        <v>47500</v>
+      </c>
+      <c r="J54" s="13"/>
+      <c r="M54" s="13"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A55" s="13">
+        <v>45961</v>
+      </c>
+      <c r="B55">
+        <v>31500</v>
+      </c>
+      <c r="C55">
+        <v>22200</v>
+      </c>
+      <c r="D55" s="14"/>
+      <c r="E55">
+        <v>14800</v>
+      </c>
+      <c r="F55">
+        <v>16100</v>
+      </c>
+      <c r="G55" s="14"/>
+      <c r="H55">
+        <v>46900</v>
+      </c>
+      <c r="J55" s="13"/>
+      <c r="M55" s="13"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A56" s="13">
+        <v>45991</v>
+      </c>
+      <c r="B56">
+        <v>30800</v>
+      </c>
+      <c r="C56">
+        <v>22200</v>
+      </c>
+      <c r="D56" s="14"/>
+      <c r="E56">
+        <v>14800</v>
+      </c>
+      <c r="F56">
+        <v>16600</v>
+      </c>
+      <c r="G56" s="14"/>
+      <c r="H56">
+        <v>46200</v>
+      </c>
+      <c r="J56" s="13"/>
+      <c r="M56" s="13"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A57" s="13">
+        <v>46022</v>
+      </c>
+      <c r="B57">
+        <v>29900</v>
+      </c>
+      <c r="C57">
+        <v>18100</v>
+      </c>
+      <c r="D57" s="14"/>
+      <c r="E57">
+        <v>12100</v>
+      </c>
+      <c r="F57">
+        <v>17200</v>
+      </c>
+      <c r="G57" s="14"/>
+      <c r="H57">
+        <v>47100</v>
+      </c>
+      <c r="J57" s="13"/>
+      <c r="M57" s="13"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A58" s="13">
+        <v>46053</v>
+      </c>
+      <c r="B58">
+        <v>33200</v>
+      </c>
+      <c r="C58">
+        <v>22200</v>
+      </c>
+      <c r="D58" s="14"/>
+      <c r="E58">
+        <v>12100</v>
+      </c>
+      <c r="F58">
+        <v>17900</v>
+      </c>
+      <c r="G58" s="14"/>
+      <c r="H58">
+        <v>49300</v>
+      </c>
+      <c r="J58" s="13"/>
+      <c r="M58" s="13"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A59" s="13">
+        <v>46081</v>
+      </c>
+      <c r="B59">
+        <v>31800</v>
+      </c>
+      <c r="C59">
+        <v>18100</v>
+      </c>
+      <c r="D59" s="14"/>
+      <c r="E59">
+        <v>14800</v>
+      </c>
+      <c r="F59">
+        <v>17400</v>
+      </c>
+      <c r="G59" s="14"/>
+      <c r="H59">
+        <v>48100</v>
+      </c>
+      <c r="J59" s="13"/>
+      <c r="M59" s="13"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A60" s="13">
+        <v>46112</v>
+      </c>
+      <c r="B60">
+        <v>31200</v>
+      </c>
+      <c r="C60">
+        <v>22200</v>
+      </c>
+      <c r="D60" s="14"/>
+      <c r="E60">
+        <v>14800</v>
+      </c>
+      <c r="F60">
+        <v>18500</v>
+      </c>
+      <c r="G60" s="14"/>
+      <c r="H60">
+        <v>49500</v>
+      </c>
+      <c r="J60" s="13"/>
+      <c r="M60" s="13"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A61" s="13">
+        <v>46142</v>
+      </c>
+      <c r="B61">
+        <v>30500</v>
+      </c>
+      <c r="C61">
+        <v>22200</v>
+      </c>
+      <c r="D61" s="14"/>
+      <c r="E61">
+        <v>14800</v>
+      </c>
+      <c r="F61">
+        <v>16200</v>
+      </c>
+      <c r="G61" s="14"/>
+      <c r="H61">
+        <v>48600</v>
+      </c>
+      <c r="J61" s="13"/>
+      <c r="M61" s="13"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="C62" s="14"/>
+      <c r="D62" s="14"/>
+      <c r="G62" s="14"/>
+      <c r="H62" s="14"/>
+      <c r="J62" s="13"/>
+      <c r="M62" s="13"/>
+      <c r="N62" s="13"/>
+      <c r="O62" s="14"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="C63" s="14"/>
+      <c r="D63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14"/>
+      <c r="K63" s="13"/>
+      <c r="M63" s="13"/>
+      <c r="N63" s="13"/>
+      <c r="O63" s="13"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="D64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="H64" s="14"/>
+      <c r="N64" s="13"/>
+    </row>
+    <row r="65" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N65" s="13"/>
+    </row>
+    <row r="66" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N66" s="13"/>
+    </row>
+    <row r="67" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N67" s="13"/>
+    </row>
+    <row r="68" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N68" s="13"/>
+    </row>
+    <row r="69" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N69" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A8B1AF-078B-4A73-8E79-1A3A32CEB8A3}">
+  <dimension ref="D1:G62"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D2">
+        <v>2021</v>
+      </c>
+      <c r="E2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2" t="str">
+        <f>_xlfn.CONCAT(D2, " ", E2)</f>
+        <v>2021 April</v>
+      </c>
+      <c r="G2">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="3" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D3">
+        <v>2021</v>
+      </c>
+      <c r="E3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F62" si="0">_xlfn.CONCAT(D3, " ", E3)</f>
+        <v>2021 May</v>
+      </c>
+      <c r="G3">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="4" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D4">
+        <v>2021</v>
+      </c>
+      <c r="E4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v>2021 June</v>
+      </c>
+      <c r="G4">
+        <v>138000</v>
+      </c>
+    </row>
+    <row r="5" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D5">
+        <v>2021</v>
+      </c>
+      <c r="E5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v>2021 July</v>
+      </c>
+      <c r="G5">
+        <v>145000</v>
+      </c>
+    </row>
+    <row r="6" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D6">
+        <v>2021</v>
+      </c>
+      <c r="E6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v>2021 August</v>
+      </c>
+      <c r="G6">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="7" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D7">
+        <v>2021</v>
+      </c>
+      <c r="E7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v>2021 September</v>
+      </c>
+      <c r="G7">
+        <v>148000</v>
+      </c>
+    </row>
+    <row r="8" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D8">
+        <v>2021</v>
+      </c>
+      <c r="E8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v>2021 October</v>
+      </c>
+      <c r="G8">
+        <v>155000</v>
+      </c>
+    </row>
+    <row r="9" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D9">
+        <v>2021</v>
+      </c>
+      <c r="E9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v>2021 November</v>
+      </c>
+      <c r="G9">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="10" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D10">
+        <v>2021</v>
+      </c>
+      <c r="E10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="0"/>
+        <v>2021 December</v>
+      </c>
+      <c r="G10">
+        <v>158000</v>
+      </c>
+    </row>
+    <row r="11" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D11">
+        <v>2022</v>
+      </c>
+      <c r="E11" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="0"/>
+        <v>2022 January</v>
+      </c>
+      <c r="G11">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="12" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D12">
+        <v>2022</v>
+      </c>
+      <c r="E12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F12" t="str">
+        <f t="shared" si="0"/>
+        <v>2022 February</v>
+      </c>
+      <c r="G12">
+        <v>175000</v>
+      </c>
+    </row>
+    <row r="13" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D13">
+        <v>2022</v>
+      </c>
+      <c r="E13" t="s">
+        <v>149</v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="0"/>
+        <v>2022 March</v>
+      </c>
+      <c r="G13">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="14" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D14">
+        <v>2022</v>
+      </c>
+      <c r="E14" t="s">
+        <v>139</v>
+      </c>
+      <c r="F14" t="str">
+        <f t="shared" si="0"/>
+        <v>2022 April</v>
+      </c>
+      <c r="G14">
+        <v>201000</v>
+      </c>
+    </row>
+    <row r="15" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D15">
+        <v>2022</v>
+      </c>
+      <c r="E15" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" t="str">
+        <f t="shared" si="0"/>
+        <v>2022 May</v>
+      </c>
+      <c r="G15">
+        <v>210000</v>
+      </c>
+    </row>
+    <row r="16" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D16">
+        <v>2022</v>
+      </c>
+      <c r="E16" t="s">
+        <v>140</v>
+      </c>
+      <c r="F16" t="str">
+        <f t="shared" si="0"/>
+        <v>2022 June</v>
+      </c>
+      <c r="G16">
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="17" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D17">
+        <v>2022</v>
+      </c>
+      <c r="E17" t="s">
+        <v>141</v>
+      </c>
+      <c r="F17" t="str">
+        <f t="shared" si="0"/>
+        <v>2022 July</v>
+      </c>
+      <c r="G17">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D18">
+        <v>2022</v>
+      </c>
+      <c r="E18" t="s">
+        <v>142</v>
+      </c>
+      <c r="F18" t="str">
+        <f t="shared" si="0"/>
+        <v>2022 August</v>
+      </c>
+      <c r="G18">
+        <v>255000</v>
+      </c>
+    </row>
+    <row r="19" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D19">
+        <v>2022</v>
+      </c>
+      <c r="E19" t="s">
+        <v>143</v>
+      </c>
+      <c r="F19" t="str">
+        <f t="shared" si="0"/>
+        <v>2022 September</v>
+      </c>
+      <c r="G19">
+        <v>270000</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D20">
+        <v>2022</v>
+      </c>
+      <c r="E20" t="s">
+        <v>144</v>
+      </c>
+      <c r="F20" t="str">
+        <f t="shared" si="0"/>
+        <v>2022 October</v>
+      </c>
+      <c r="G20">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="21" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D21">
+        <v>2022</v>
+      </c>
+      <c r="E21" t="s">
+        <v>145</v>
+      </c>
+      <c r="F21" t="str">
+        <f t="shared" si="0"/>
+        <v>2022 November</v>
+      </c>
+      <c r="G21">
+        <v>310000</v>
+      </c>
+    </row>
+    <row r="22" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D22">
+        <v>2022</v>
+      </c>
+      <c r="E22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F22" t="str">
+        <f t="shared" si="0"/>
+        <v>2022 December</v>
+      </c>
+      <c r="G22">
+        <v>290000</v>
+      </c>
+    </row>
+    <row r="23" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D23">
+        <v>2023</v>
+      </c>
+      <c r="E23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F23" t="str">
+        <f t="shared" si="0"/>
+        <v>2023 January</v>
+      </c>
+      <c r="G23">
+        <v>330000</v>
+      </c>
+    </row>
+    <row r="24" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D24">
+        <v>2023</v>
+      </c>
+      <c r="E24" t="s">
+        <v>148</v>
+      </c>
+      <c r="F24" t="str">
+        <f t="shared" si="0"/>
+        <v>2023 February</v>
+      </c>
+      <c r="G24">
+        <v>315000</v>
+      </c>
+    </row>
+    <row r="25" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D25">
+        <v>2023</v>
+      </c>
+      <c r="E25" t="s">
+        <v>149</v>
+      </c>
+      <c r="F25" t="str">
+        <f t="shared" si="0"/>
+        <v>2023 March</v>
+      </c>
+      <c r="G25">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="26" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D26">
+        <v>2023</v>
+      </c>
+      <c r="E26" t="s">
+        <v>139</v>
+      </c>
+      <c r="F26" t="str">
+        <f t="shared" si="0"/>
+        <v>2023 April</v>
+      </c>
+      <c r="G26">
+        <v>340000</v>
+      </c>
+    </row>
+    <row r="27" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D27">
+        <v>2023</v>
+      </c>
+      <c r="E27" t="s">
+        <v>125</v>
+      </c>
+      <c r="F27" t="str">
+        <f t="shared" si="0"/>
+        <v>2023 May</v>
+      </c>
+      <c r="G27">
+        <v>330000</v>
+      </c>
+    </row>
+    <row r="28" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D28">
+        <v>2023</v>
+      </c>
+      <c r="E28" t="s">
+        <v>140</v>
+      </c>
+      <c r="F28" t="str">
+        <f t="shared" si="0"/>
+        <v>2023 June</v>
+      </c>
+      <c r="G28">
+        <v>320000</v>
+      </c>
+    </row>
+    <row r="29" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D29">
+        <v>2023</v>
+      </c>
+      <c r="E29" t="s">
+        <v>141</v>
+      </c>
+      <c r="F29" t="str">
+        <f t="shared" si="0"/>
+        <v>2023 July</v>
+      </c>
+      <c r="G29">
+        <v>345000</v>
+      </c>
+    </row>
+    <row r="30" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D30">
+        <v>2023</v>
+      </c>
+      <c r="E30" t="s">
+        <v>142</v>
+      </c>
+      <c r="F30" t="str">
+        <f t="shared" si="0"/>
+        <v>2023 August</v>
+      </c>
+      <c r="G30">
+        <v>360000</v>
+      </c>
+    </row>
+    <row r="31" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D31">
+        <v>2023</v>
+      </c>
+      <c r="E31" t="s">
+        <v>143</v>
+      </c>
+      <c r="F31" t="str">
+        <f t="shared" si="0"/>
+        <v>2023 September</v>
+      </c>
+      <c r="G31">
+        <v>355000</v>
+      </c>
+    </row>
+    <row r="32" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D32">
+        <v>2023</v>
+      </c>
+      <c r="E32" t="s">
+        <v>144</v>
+      </c>
+      <c r="F32" t="str">
+        <f t="shared" si="0"/>
+        <v>2023 October</v>
+      </c>
+      <c r="G32">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="33" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D33">
+        <v>2023</v>
+      </c>
+      <c r="E33" t="s">
+        <v>145</v>
+      </c>
+      <c r="F33" t="str">
+        <f t="shared" si="0"/>
+        <v>2023 November</v>
+      </c>
+      <c r="G33">
+        <v>365000</v>
+      </c>
+    </row>
+    <row r="34" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D34">
+        <v>2023</v>
+      </c>
+      <c r="E34" t="s">
+        <v>146</v>
+      </c>
+      <c r="F34" t="str">
+        <f t="shared" si="0"/>
+        <v>2023 December</v>
+      </c>
+      <c r="G34">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="35" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D35">
+        <v>2024</v>
+      </c>
+      <c r="E35" t="s">
+        <v>147</v>
+      </c>
+      <c r="F35" t="str">
+        <f t="shared" si="0"/>
+        <v>2024 January</v>
+      </c>
+      <c r="G35">
+        <v>390000</v>
+      </c>
+    </row>
+    <row r="36" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D36">
+        <v>2024</v>
+      </c>
+      <c r="E36" t="s">
+        <v>148</v>
+      </c>
+      <c r="F36" t="str">
+        <f t="shared" si="0"/>
+        <v>2024 February</v>
+      </c>
+      <c r="G36">
+        <v>380000</v>
+      </c>
+    </row>
+    <row r="37" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D37">
+        <v>2024</v>
+      </c>
+      <c r="E37" t="s">
+        <v>149</v>
+      </c>
+      <c r="F37" t="str">
+        <f t="shared" si="0"/>
+        <v>2024 March</v>
+      </c>
+      <c r="G37">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="38" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D38">
+        <v>2024</v>
+      </c>
+      <c r="E38" t="s">
+        <v>139</v>
+      </c>
+      <c r="F38" t="str">
+        <f t="shared" si="0"/>
+        <v>2024 April</v>
+      </c>
+      <c r="G38">
+        <v>395000</v>
+      </c>
+    </row>
+    <row r="39" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D39">
+        <v>2024</v>
+      </c>
+      <c r="E39" t="s">
+        <v>125</v>
+      </c>
+      <c r="F39" t="str">
+        <f t="shared" si="0"/>
+        <v>2024 May</v>
+      </c>
+      <c r="G39">
+        <v>385000</v>
+      </c>
+    </row>
+    <row r="40" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D40">
+        <v>2024</v>
+      </c>
+      <c r="E40" t="s">
+        <v>140</v>
+      </c>
+      <c r="F40" t="str">
+        <f t="shared" si="0"/>
+        <v>2024 June</v>
+      </c>
+      <c r="G40">
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="41" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D41">
+        <v>2024</v>
+      </c>
+      <c r="E41" t="s">
+        <v>141</v>
+      </c>
+      <c r="F41" t="str">
+        <f t="shared" si="0"/>
+        <v>2024 July</v>
+      </c>
+      <c r="G41">
+        <v>390000</v>
+      </c>
+    </row>
+    <row r="42" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D42">
+        <v>2024</v>
+      </c>
+      <c r="E42" t="s">
+        <v>142</v>
+      </c>
+      <c r="F42" t="str">
+        <f t="shared" si="0"/>
+        <v>2024 August</v>
+      </c>
+      <c r="G42">
+        <v>410000</v>
+      </c>
+    </row>
+    <row r="43" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D43">
+        <v>2024</v>
+      </c>
+      <c r="E43" t="s">
+        <v>143</v>
+      </c>
+      <c r="F43" t="str">
+        <f t="shared" si="0"/>
+        <v>2024 September</v>
+      </c>
+      <c r="G43">
+        <v>405000</v>
+      </c>
+    </row>
+    <row r="44" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D44">
+        <v>2024</v>
+      </c>
+      <c r="E44" t="s">
+        <v>144</v>
+      </c>
+      <c r="F44" t="str">
+        <f t="shared" si="0"/>
+        <v>2024 October</v>
+      </c>
+      <c r="G44">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="45" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D45">
+        <v>2024</v>
+      </c>
+      <c r="E45" t="s">
+        <v>145</v>
+      </c>
+      <c r="F45" t="str">
+        <f t="shared" si="0"/>
+        <v>2024 November</v>
+      </c>
+      <c r="G45">
+        <v>415000</v>
+      </c>
+    </row>
+    <row r="46" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D46">
+        <v>2024</v>
+      </c>
+      <c r="E46" t="s">
+        <v>146</v>
+      </c>
+      <c r="F46" t="str">
+        <f t="shared" si="0"/>
+        <v>2024 December</v>
+      </c>
+      <c r="G46">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="47" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D47">
+        <v>2025</v>
+      </c>
+      <c r="E47" t="s">
+        <v>147</v>
+      </c>
+      <c r="F47" t="str">
+        <f t="shared" si="0"/>
+        <v>2025 January</v>
+      </c>
+      <c r="G47">
+        <v>440000</v>
+      </c>
+    </row>
+    <row r="48" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D48">
+        <v>2025</v>
+      </c>
+      <c r="E48" t="s">
+        <v>148</v>
+      </c>
+      <c r="F48" t="str">
+        <f t="shared" si="0"/>
+        <v>2025 February</v>
+      </c>
+      <c r="G48">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="49" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D49">
+        <v>2025</v>
+      </c>
+      <c r="E49" t="s">
+        <v>149</v>
+      </c>
+      <c r="F49" t="str">
+        <f t="shared" si="0"/>
+        <v>2025 March</v>
+      </c>
+      <c r="G49">
+        <v>455000</v>
+      </c>
+    </row>
+    <row r="50" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D50">
+        <v>2025</v>
+      </c>
+      <c r="E50" t="s">
+        <v>139</v>
+      </c>
+      <c r="F50" t="str">
+        <f t="shared" si="0"/>
+        <v>2025 April</v>
+      </c>
+      <c r="G50">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="51" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D51">
+        <v>2025</v>
+      </c>
+      <c r="E51" t="s">
+        <v>125</v>
+      </c>
+      <c r="F51" t="str">
+        <f t="shared" si="0"/>
+        <v>2025 May</v>
+      </c>
+      <c r="G51">
+        <v>440000</v>
+      </c>
+    </row>
+    <row r="52" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D52">
+        <v>2025</v>
+      </c>
+      <c r="E52" t="s">
+        <v>140</v>
+      </c>
+      <c r="F52" t="str">
+        <f t="shared" si="0"/>
+        <v>2025 June</v>
+      </c>
+      <c r="G52">
+        <v>435000</v>
+      </c>
+    </row>
+    <row r="53" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D53">
+        <v>2025</v>
+      </c>
+      <c r="E53" t="s">
+        <v>141</v>
+      </c>
+      <c r="F53" t="str">
+        <f t="shared" si="0"/>
+        <v>2025 July</v>
+      </c>
+      <c r="G53">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="54" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D54">
+        <v>2025</v>
+      </c>
+      <c r="E54" t="s">
+        <v>142</v>
+      </c>
+      <c r="F54" t="str">
+        <f t="shared" si="0"/>
+        <v>2025 August</v>
+      </c>
+      <c r="G54">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="55" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D55">
+        <v>2025</v>
+      </c>
+      <c r="E55" t="s">
+        <v>143</v>
+      </c>
+      <c r="F55" t="str">
+        <f t="shared" si="0"/>
+        <v>2025 September</v>
+      </c>
+      <c r="G55">
+        <v>465000</v>
+      </c>
+    </row>
+    <row r="56" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D56">
+        <v>2025</v>
+      </c>
+      <c r="E56" t="s">
+        <v>144</v>
+      </c>
+      <c r="F56" t="str">
+        <f t="shared" si="0"/>
+        <v>2025 October</v>
+      </c>
+      <c r="G56">
+        <v>480000</v>
+      </c>
+    </row>
+    <row r="57" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D57">
+        <v>2025</v>
+      </c>
+      <c r="E57" t="s">
+        <v>145</v>
+      </c>
+      <c r="F57" t="str">
+        <f t="shared" si="0"/>
+        <v>2025 November</v>
+      </c>
+      <c r="G57">
+        <v>475000</v>
+      </c>
+    </row>
+    <row r="58" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D58">
+        <v>2025</v>
+      </c>
+      <c r="E58" t="s">
+        <v>146</v>
+      </c>
+      <c r="F58" t="str">
+        <f t="shared" si="0"/>
+        <v>2025 December</v>
+      </c>
+      <c r="G58">
+        <v>460000</v>
+      </c>
+    </row>
+    <row r="59" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D59">
+        <v>2026</v>
+      </c>
+      <c r="E59" t="s">
+        <v>147</v>
+      </c>
+      <c r="F59" t="str">
+        <f t="shared" si="0"/>
+        <v>2026 January</v>
+      </c>
+      <c r="G59">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="60" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D60">
+        <v>2026</v>
+      </c>
+      <c r="E60" t="s">
+        <v>148</v>
+      </c>
+      <c r="F60" t="str">
+        <f t="shared" si="0"/>
+        <v>2026 February</v>
+      </c>
+      <c r="G60">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="61" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D61">
+        <v>2026</v>
+      </c>
+      <c r="E61" t="s">
+        <v>149</v>
+      </c>
+      <c r="F61" t="str">
+        <f t="shared" si="0"/>
+        <v>2026 March</v>
+      </c>
+      <c r="G61">
+        <v>510000</v>
+      </c>
+    </row>
+    <row r="62" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D62">
+        <v>2026</v>
+      </c>
+      <c r="E62" t="s">
+        <v>139</v>
+      </c>
+      <c r="F62" t="str">
+        <f t="shared" si="0"/>
+        <v>2026 April</v>
+      </c>
+      <c r="G62">
+        <v>505000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{343083D1-5AAF-47F8-9074-8D746FC802B2}">
+  <dimension ref="B2:C7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B2" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B3" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B4" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B5" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B6" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B7" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ms_teams_copilot_client_answers.xlsx
+++ b/ms_teams_copilot_client_answers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohitVerma\Desktop\git\translation\SaS-to-python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB645F27-3797-4993-964A-D9DD09B5FAFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BAE94EB-60A4-423B-B914-5A266A83621C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quick Summary" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="169">
   <si>
     <t>Quick summary for the client</t>
   </si>
@@ -664,6 +664,33 @@
  Summarize insights in 1–2 paragraphs highlighting what drives discussion volume (e.g., promotions, rate cuts, scandals, or UX)._x000D_
 _x000D_
 Return the final output as a **Markdown table**. _x000D_</t>
+  </si>
+  <si>
+    <t>Jp Morgan</t>
+  </si>
+  <si>
+    <t>Amex</t>
+  </si>
+  <si>
+    <t>Citi</t>
+  </si>
+  <si>
+    <t>Bank of America</t>
+  </si>
+  <si>
+    <t>Wells Fargo</t>
+  </si>
+  <si>
+    <t>US Bank</t>
+  </si>
+  <si>
+    <t>Goldman Sachs</t>
+  </si>
+  <si>
+    <t>USAA</t>
+  </si>
+  <si>
+    <t>PNC Bank</t>
   </si>
 </sst>
 </file>
@@ -811,7 +838,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -849,6 +876,7 @@
     <xf numFmtId="15" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -859,7 +887,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2400,22 +2433,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
     </row>
     <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
     </row>
     <row r="4" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -2613,40 +2646,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
     </row>
     <row r="4" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -2932,24 +2965,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -3023,7 +3056,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCE9345-FC91-4D0C-9835-473AC28707EE}">
-  <dimension ref="B2:L12"/>
+  <dimension ref="B2:N29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="16.08984375" bestFit="1" customWidth="1"/>
@@ -3420,8 +3453,549 @@
         <v>0</v>
       </c>
     </row>
+    <row r="17" spans="2:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="B17" s="20"/>
+      <c r="C17" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="J17" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="M17" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="N17" s="21" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B18" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" s="10">
+        <v>0</v>
+      </c>
+      <c r="D18" s="10">
+        <v>96</v>
+      </c>
+      <c r="E18" s="10">
+        <v>92</v>
+      </c>
+      <c r="F18" s="10">
+        <v>85</v>
+      </c>
+      <c r="G18" s="10">
+        <v>81</v>
+      </c>
+      <c r="H18" s="10">
+        <v>77</v>
+      </c>
+      <c r="I18" s="10">
+        <v>65</v>
+      </c>
+      <c r="J18" s="10">
+        <v>58</v>
+      </c>
+      <c r="K18" s="10">
+        <v>42</v>
+      </c>
+      <c r="L18" s="10">
+        <v>40</v>
+      </c>
+      <c r="M18" s="10">
+        <v>31</v>
+      </c>
+      <c r="N18" s="10">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B19" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="C19" s="10">
+        <v>96</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10">
+        <v>89</v>
+      </c>
+      <c r="F19" s="10">
+        <v>83</v>
+      </c>
+      <c r="G19" s="10">
+        <v>78</v>
+      </c>
+      <c r="H19" s="10">
+        <v>75</v>
+      </c>
+      <c r="I19" s="10">
+        <v>60</v>
+      </c>
+      <c r="J19" s="10">
+        <v>63</v>
+      </c>
+      <c r="K19" s="10">
+        <v>38</v>
+      </c>
+      <c r="L19" s="10">
+        <v>51</v>
+      </c>
+      <c r="M19" s="10">
+        <v>33</v>
+      </c>
+      <c r="N19" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B20" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="10">
+        <v>92</v>
+      </c>
+      <c r="D20" s="10">
+        <v>89</v>
+      </c>
+      <c r="E20" s="10">
+        <v>0</v>
+      </c>
+      <c r="F20" s="10">
+        <v>80</v>
+      </c>
+      <c r="G20" s="10">
+        <v>87</v>
+      </c>
+      <c r="H20" s="10">
+        <v>79</v>
+      </c>
+      <c r="I20" s="10">
+        <v>69</v>
+      </c>
+      <c r="J20" s="10">
+        <v>61</v>
+      </c>
+      <c r="K20" s="10">
+        <v>65</v>
+      </c>
+      <c r="L20" s="10">
+        <v>42</v>
+      </c>
+      <c r="M20" s="10">
+        <v>36</v>
+      </c>
+      <c r="N20" s="10">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B21" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C21" s="10">
+        <v>85</v>
+      </c>
+      <c r="D21" s="10">
+        <v>83</v>
+      </c>
+      <c r="E21" s="10">
+        <v>80</v>
+      </c>
+      <c r="F21" s="10">
+        <v>0</v>
+      </c>
+      <c r="G21" s="10">
+        <v>74</v>
+      </c>
+      <c r="H21" s="10">
+        <v>72</v>
+      </c>
+      <c r="I21" s="10">
+        <v>62</v>
+      </c>
+      <c r="J21" s="10">
+        <v>56</v>
+      </c>
+      <c r="K21" s="10">
+        <v>40</v>
+      </c>
+      <c r="L21" s="10">
+        <v>38</v>
+      </c>
+      <c r="M21" s="10">
+        <v>24</v>
+      </c>
+      <c r="N21" s="10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B22" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="C22" s="10">
+        <v>81</v>
+      </c>
+      <c r="D22" s="10">
+        <v>78</v>
+      </c>
+      <c r="E22" s="10">
+        <v>87</v>
+      </c>
+      <c r="F22" s="10">
+        <v>74</v>
+      </c>
+      <c r="G22" s="10">
+        <v>0</v>
+      </c>
+      <c r="H22" s="10">
+        <v>83</v>
+      </c>
+      <c r="I22" s="10">
+        <v>71</v>
+      </c>
+      <c r="J22" s="10">
+        <v>53</v>
+      </c>
+      <c r="K22" s="10">
+        <v>49</v>
+      </c>
+      <c r="L22" s="10">
+        <v>35</v>
+      </c>
+      <c r="M22" s="10">
+        <v>47</v>
+      </c>
+      <c r="N22" s="10">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B23" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C23" s="10">
+        <v>77</v>
+      </c>
+      <c r="D23" s="10">
+        <v>75</v>
+      </c>
+      <c r="E23" s="10">
+        <v>79</v>
+      </c>
+      <c r="F23" s="10">
+        <v>72</v>
+      </c>
+      <c r="G23" s="10">
+        <v>83</v>
+      </c>
+      <c r="H23" s="10">
+        <v>0</v>
+      </c>
+      <c r="I23" s="10">
+        <v>67</v>
+      </c>
+      <c r="J23" s="10">
+        <v>49</v>
+      </c>
+      <c r="K23" s="10">
+        <v>44</v>
+      </c>
+      <c r="L23" s="10">
+        <v>33</v>
+      </c>
+      <c r="M23" s="10">
+        <v>40</v>
+      </c>
+      <c r="N23" s="10">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B24" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" s="10">
+        <v>65</v>
+      </c>
+      <c r="D24" s="10">
+        <v>60</v>
+      </c>
+      <c r="E24" s="10">
+        <v>69</v>
+      </c>
+      <c r="F24" s="10">
+        <v>62</v>
+      </c>
+      <c r="G24" s="10">
+        <v>71</v>
+      </c>
+      <c r="H24" s="10">
+        <v>67</v>
+      </c>
+      <c r="I24" s="10">
+        <v>0</v>
+      </c>
+      <c r="J24" s="10">
+        <v>44</v>
+      </c>
+      <c r="K24" s="10">
+        <v>47</v>
+      </c>
+      <c r="L24" s="10">
+        <v>27</v>
+      </c>
+      <c r="M24" s="10">
+        <v>35</v>
+      </c>
+      <c r="N24" s="10">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B25" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C25" s="10">
+        <v>58</v>
+      </c>
+      <c r="D25" s="10">
+        <v>63</v>
+      </c>
+      <c r="E25" s="10">
+        <v>61</v>
+      </c>
+      <c r="F25" s="10">
+        <v>56</v>
+      </c>
+      <c r="G25" s="10">
+        <v>53</v>
+      </c>
+      <c r="H25" s="10">
+        <v>49</v>
+      </c>
+      <c r="I25" s="10">
+        <v>44</v>
+      </c>
+      <c r="J25" s="10">
+        <v>0</v>
+      </c>
+      <c r="K25" s="10">
+        <v>51</v>
+      </c>
+      <c r="L25" s="10">
+        <v>47</v>
+      </c>
+      <c r="M25" s="10">
+        <v>18</v>
+      </c>
+      <c r="N25" s="10">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B26" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="10">
+        <v>42</v>
+      </c>
+      <c r="D26" s="10">
+        <v>38</v>
+      </c>
+      <c r="E26" s="10">
+        <v>65</v>
+      </c>
+      <c r="F26" s="10">
+        <v>40</v>
+      </c>
+      <c r="G26" s="10">
+        <v>49</v>
+      </c>
+      <c r="H26" s="10">
+        <v>44</v>
+      </c>
+      <c r="I26" s="10">
+        <v>47</v>
+      </c>
+      <c r="J26" s="10">
+        <v>51</v>
+      </c>
+      <c r="K26" s="10">
+        <v>0</v>
+      </c>
+      <c r="L26" s="10">
+        <v>31</v>
+      </c>
+      <c r="M26" s="10">
+        <v>15</v>
+      </c>
+      <c r="N26" s="10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B27" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="C27" s="10">
+        <v>40</v>
+      </c>
+      <c r="D27" s="10">
+        <v>51</v>
+      </c>
+      <c r="E27" s="10">
+        <v>42</v>
+      </c>
+      <c r="F27" s="10">
+        <v>38</v>
+      </c>
+      <c r="G27" s="10">
+        <v>35</v>
+      </c>
+      <c r="H27" s="10">
+        <v>33</v>
+      </c>
+      <c r="I27" s="10">
+        <v>27</v>
+      </c>
+      <c r="J27" s="10">
+        <v>47</v>
+      </c>
+      <c r="K27" s="10">
+        <v>31</v>
+      </c>
+      <c r="L27" s="10">
+        <v>0</v>
+      </c>
+      <c r="M27" s="10">
+        <v>13</v>
+      </c>
+      <c r="N27" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B28" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" s="10">
+        <v>31</v>
+      </c>
+      <c r="D28" s="10">
+        <v>33</v>
+      </c>
+      <c r="E28" s="10">
+        <v>36</v>
+      </c>
+      <c r="F28" s="10">
+        <v>24</v>
+      </c>
+      <c r="G28" s="10">
+        <v>47</v>
+      </c>
+      <c r="H28" s="10">
+        <v>40</v>
+      </c>
+      <c r="I28" s="10">
+        <v>35</v>
+      </c>
+      <c r="J28" s="10">
+        <v>18</v>
+      </c>
+      <c r="K28" s="10">
+        <v>15</v>
+      </c>
+      <c r="L28" s="10">
+        <v>13</v>
+      </c>
+      <c r="M28" s="10">
+        <v>0</v>
+      </c>
+      <c r="N28" s="10">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B29" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C29" s="10">
+        <v>35</v>
+      </c>
+      <c r="D29" s="10">
+        <v>29</v>
+      </c>
+      <c r="E29" s="10">
+        <v>44</v>
+      </c>
+      <c r="F29" s="10">
+        <v>31</v>
+      </c>
+      <c r="G29" s="10">
+        <v>56</v>
+      </c>
+      <c r="H29" s="10">
+        <v>51</v>
+      </c>
+      <c r="I29" s="10">
+        <v>49</v>
+      </c>
+      <c r="J29" s="10">
+        <v>22</v>
+      </c>
+      <c r="K29" s="10">
+        <v>27</v>
+      </c>
+      <c r="L29" s="10">
+        <v>11</v>
+      </c>
+      <c r="M29" s="10">
+        <v>42</v>
+      </c>
+      <c r="N29" s="10">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="C3:L12">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:N29">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -5931,10 +6505,10 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="15" t="s">
         <v>152</v>
       </c>
     </row>
@@ -5947,10 +6521,10 @@
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="15" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5963,10 +6537,10 @@
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="15" t="s">
         <v>157</v>
       </c>
     </row>

--- a/ms_teams_copilot_client_answers.xlsx
+++ b/ms_teams_copilot_client_answers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohitVerma\Desktop\git\translation\SaS-to-python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BAE94EB-60A4-423B-B914-5A266A83621C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4553A32C-6C30-4071-A597-925901DCB89B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="300" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quick Summary" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="176">
   <si>
     <t>Quick summary for the client</t>
   </si>
@@ -691,6 +691,27 @@
   </si>
   <si>
     <t>PNC Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Synchrony </t>
+  </si>
+  <si>
+    <t>Gemini</t>
+  </si>
+  <si>
+    <t>Claude</t>
+  </si>
+  <si>
+    <t>JP Morgan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNC Bank </t>
+  </si>
+  <si>
+    <t>GoldmanSachs</t>
+  </si>
+  <si>
+    <t>ChatGPT</t>
   </si>
 </sst>
 </file>
@@ -877,6 +898,12 @@
       <alignment vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -886,12 +913,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2433,22 +2454,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
     </row>
     <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
     </row>
     <row r="4" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -2646,40 +2667,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
     </row>
     <row r="4" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -2965,24 +2986,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
     </row>
     <row r="2" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
     </row>
     <row r="4" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -3056,7 +3077,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCE9345-FC91-4D0C-9835-473AC28707EE}">
-  <dimension ref="B2:N29"/>
+  <dimension ref="B1:AP30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="16.08984375" bestFit="1" customWidth="1"/>
@@ -3068,924 +3089,2709 @@
     <col min="14" max="14" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.1796875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="10"/>
-      <c r="C2" s="11" t="s">
+    <row r="1" spans="2:40" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>170</v>
+      </c>
+      <c r="P1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="2:40" x14ac:dyDescent="0.35">
+      <c r="B3" s="10"/>
+      <c r="C3" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D3" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E3" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F3" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K3" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L3" s="11" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B3" s="11" t="s">
+      <c r="P3" s="10"/>
+      <c r="Q3" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="10">
+      <c r="R3" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="S3" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="T3" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="X3" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z3" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD3" s="10"/>
+      <c r="AE3" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF3" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG3" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH3" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="AI3" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="AJ3" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="AK3" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL3" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM3" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="AN3" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="2:40" x14ac:dyDescent="0.35">
+      <c r="B4" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="10">
         <v>0</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D4" s="10">
         <v>38</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E4" s="10">
         <v>58</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F4" s="10">
         <v>73</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G4" s="10">
         <v>80</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H4" s="10">
         <v>67</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I4" s="10">
         <v>60</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J4" s="10">
         <v>62</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K4" s="10">
         <v>49</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L4" s="10">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B4" s="11" t="s">
+      <c r="P4" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q4" s="10">
+        <v>0</v>
+      </c>
+      <c r="R4" s="10">
+        <v>23</v>
+      </c>
+      <c r="S4" s="10">
+        <v>93</v>
+      </c>
+      <c r="T4" s="10">
+        <v>86</v>
+      </c>
+      <c r="U4" s="10">
+        <v>73</v>
+      </c>
+      <c r="V4" s="10">
+        <v>75</v>
+      </c>
+      <c r="W4" s="10">
+        <v>50</v>
+      </c>
+      <c r="X4" s="10">
+        <v>91</v>
+      </c>
+      <c r="Y4" s="10">
+        <v>48</v>
+      </c>
+      <c r="Z4" s="10">
+        <v>21</v>
+      </c>
+      <c r="AD4" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="10">
+        <v>18</v>
+      </c>
+      <c r="AG4" s="10">
+        <v>34</v>
+      </c>
+      <c r="AH4" s="10">
+        <v>62</v>
+      </c>
+      <c r="AI4" s="10">
+        <v>88</v>
+      </c>
+      <c r="AJ4" s="10">
+        <v>76</v>
+      </c>
+      <c r="AK4" s="10">
+        <v>71</v>
+      </c>
+      <c r="AL4" s="10">
+        <v>55</v>
+      </c>
+      <c r="AM4" s="10">
+        <v>22</v>
+      </c>
+      <c r="AN4" s="10">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="2:40" x14ac:dyDescent="0.35">
+      <c r="B5" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C5" s="10">
         <v>38</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D5" s="10">
         <v>0</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E5" s="10">
         <v>40</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F5" s="10">
         <v>42</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G5" s="10">
         <v>56</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H5" s="10">
         <v>53</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I5" s="10">
         <v>64</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J5" s="10">
         <v>36</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K5" s="10">
         <v>22</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L5" s="10">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="11" t="s">
+      <c r="P5" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>23</v>
+      </c>
+      <c r="R5" s="10">
+        <v>0</v>
+      </c>
+      <c r="S5" s="10">
+        <v>28</v>
+      </c>
+      <c r="T5" s="10">
+        <v>35</v>
+      </c>
+      <c r="U5" s="10">
+        <v>44</v>
+      </c>
+      <c r="V5" s="10">
+        <v>41</v>
+      </c>
+      <c r="W5" s="10">
+        <v>39</v>
+      </c>
+      <c r="X5" s="10">
+        <v>30</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>5</v>
+      </c>
+      <c r="AD5" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>18</v>
+      </c>
+      <c r="AF5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="10">
+        <v>12</v>
+      </c>
+      <c r="AH5" s="10">
+        <v>29</v>
+      </c>
+      <c r="AI5" s="10">
+        <v>74</v>
+      </c>
+      <c r="AJ5" s="10">
+        <v>58</v>
+      </c>
+      <c r="AK5" s="10">
+        <v>66</v>
+      </c>
+      <c r="AL5" s="10">
+        <v>24</v>
+      </c>
+      <c r="AM5" s="10">
+        <v>1</v>
+      </c>
+      <c r="AN5" s="10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="2:40" x14ac:dyDescent="0.35">
+      <c r="B6" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C6" s="10">
         <v>58</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D6" s="10">
         <v>40</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E6" s="10">
         <v>0</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F6" s="10">
         <v>69</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G6" s="10">
         <v>51</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H6" s="10">
         <v>47</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I6" s="10">
         <v>44</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J6" s="10">
         <v>82</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K6" s="10">
         <v>53</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L6" s="10">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="11" t="s">
+      <c r="P6" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>93</v>
+      </c>
+      <c r="R6" s="10">
+        <v>28</v>
+      </c>
+      <c r="S6" s="10">
+        <v>0</v>
+      </c>
+      <c r="T6" s="10">
+        <v>82</v>
+      </c>
+      <c r="U6" s="10">
+        <v>57</v>
+      </c>
+      <c r="V6" s="10">
+        <v>64</v>
+      </c>
+      <c r="W6" s="10">
+        <v>59</v>
+      </c>
+      <c r="X6" s="10">
+        <v>89</v>
+      </c>
+      <c r="Y6" s="10">
+        <v>26</v>
+      </c>
+      <c r="Z6" s="10">
+        <v>8</v>
+      </c>
+      <c r="AD6" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE6" s="10">
+        <v>34</v>
+      </c>
+      <c r="AF6" s="10">
+        <v>12</v>
+      </c>
+      <c r="AG6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="10">
+        <v>44</v>
+      </c>
+      <c r="AI6" s="10">
+        <v>79</v>
+      </c>
+      <c r="AJ6" s="10">
+        <v>63</v>
+      </c>
+      <c r="AK6" s="10">
+        <v>57</v>
+      </c>
+      <c r="AL6" s="10">
+        <v>41</v>
+      </c>
+      <c r="AM6" s="10">
+        <v>15</v>
+      </c>
+      <c r="AN6" s="10">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="2:40" x14ac:dyDescent="0.35">
+      <c r="B7" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C7" s="10">
         <v>73</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D7" s="10">
         <v>42</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E7" s="10">
         <v>69</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F7" s="10">
         <v>0</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G7" s="10">
         <v>84</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H7" s="10">
         <v>78</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I7" s="10">
         <v>71</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J7" s="10">
         <v>60</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K7" s="10">
         <v>47</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L7" s="10">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="11" t="s">
+      <c r="P7" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>86</v>
+      </c>
+      <c r="R7" s="10">
+        <v>35</v>
+      </c>
+      <c r="S7" s="10">
+        <v>82</v>
+      </c>
+      <c r="T7" s="10">
+        <v>0</v>
+      </c>
+      <c r="U7" s="10">
+        <v>71</v>
+      </c>
+      <c r="V7" s="10">
+        <v>66</v>
+      </c>
+      <c r="W7" s="10">
+        <v>62</v>
+      </c>
+      <c r="X7" s="10">
+        <v>84</v>
+      </c>
+      <c r="Y7" s="10">
+        <v>19</v>
+      </c>
+      <c r="Z7" s="10">
+        <v>37</v>
+      </c>
+      <c r="AD7" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="AE7" s="10">
+        <v>62</v>
+      </c>
+      <c r="AF7" s="10">
+        <v>29</v>
+      </c>
+      <c r="AG7" s="10">
+        <v>44</v>
+      </c>
+      <c r="AH7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="10">
+        <v>95</v>
+      </c>
+      <c r="AJ7" s="10">
+        <v>82</v>
+      </c>
+      <c r="AK7" s="10">
+        <v>77</v>
+      </c>
+      <c r="AL7" s="10">
+        <v>69</v>
+      </c>
+      <c r="AM7" s="10">
+        <v>27</v>
+      </c>
+      <c r="AN7" s="10">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="2:40" x14ac:dyDescent="0.35">
+      <c r="B8" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C8" s="10">
         <v>80</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D8" s="10">
         <v>56</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E8" s="10">
         <v>51</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F8" s="10">
         <v>84</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G8" s="10">
         <v>0</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H8" s="10">
         <v>98</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I8" s="10">
         <v>96</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J8" s="10">
         <v>76</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K8" s="10">
         <v>42</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L8" s="10">
         <v>62</v>
       </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="11" t="s">
+      <c r="P8" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>73</v>
+      </c>
+      <c r="R8" s="10">
+        <v>44</v>
+      </c>
+      <c r="S8" s="10">
+        <v>57</v>
+      </c>
+      <c r="T8" s="10">
+        <v>71</v>
+      </c>
+      <c r="U8" s="10">
+        <v>0</v>
+      </c>
+      <c r="V8" s="10">
+        <v>100</v>
+      </c>
+      <c r="W8" s="10">
+        <v>98</v>
+      </c>
+      <c r="X8" s="10">
+        <v>77</v>
+      </c>
+      <c r="Y8" s="10">
+        <v>17</v>
+      </c>
+      <c r="Z8" s="10">
+        <v>53</v>
+      </c>
+      <c r="AD8" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE8" s="10">
+        <v>88</v>
+      </c>
+      <c r="AF8" s="10">
+        <v>74</v>
+      </c>
+      <c r="AG8" s="10">
+        <v>79</v>
+      </c>
+      <c r="AH8" s="10">
+        <v>95</v>
+      </c>
+      <c r="AI8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="10">
+        <v>100</v>
+      </c>
+      <c r="AK8" s="10">
+        <v>97</v>
+      </c>
+      <c r="AL8" s="10">
+        <v>84</v>
+      </c>
+      <c r="AM8" s="10">
+        <v>49</v>
+      </c>
+      <c r="AN8" s="10">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="2:40" x14ac:dyDescent="0.35">
+      <c r="B9" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C9" s="10">
         <v>67</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D9" s="10">
         <v>53</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E9" s="10">
         <v>47</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F9" s="10">
         <v>78</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G9" s="10">
         <v>98</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H9" s="10">
         <v>0</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I9" s="10">
         <v>93</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J9" s="10">
         <v>56</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K9" s="10">
         <v>31</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L9" s="10">
         <v>71</v>
       </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B9" s="11" t="s">
+      <c r="P9" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>75</v>
+      </c>
+      <c r="R9" s="10">
+        <v>41</v>
+      </c>
+      <c r="S9" s="10">
+        <v>64</v>
+      </c>
+      <c r="T9" s="10">
+        <v>66</v>
+      </c>
+      <c r="U9" s="10">
+        <v>100</v>
+      </c>
+      <c r="V9" s="10">
+        <v>0</v>
+      </c>
+      <c r="W9" s="10">
+        <v>95</v>
+      </c>
+      <c r="X9" s="10">
+        <v>80</v>
+      </c>
+      <c r="Y9" s="10">
+        <v>14</v>
+      </c>
+      <c r="Z9" s="10">
+        <v>55</v>
+      </c>
+      <c r="AD9" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE9" s="10">
+        <v>76</v>
+      </c>
+      <c r="AF9" s="10">
+        <v>58</v>
+      </c>
+      <c r="AG9" s="10">
+        <v>63</v>
+      </c>
+      <c r="AH9" s="10">
+        <v>82</v>
+      </c>
+      <c r="AI9" s="10">
+        <v>100</v>
+      </c>
+      <c r="AJ9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="10">
+        <v>92</v>
+      </c>
+      <c r="AL9" s="10">
+        <v>73</v>
+      </c>
+      <c r="AM9" s="10">
+        <v>39</v>
+      </c>
+      <c r="AN9" s="10">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="2:40" x14ac:dyDescent="0.35">
+      <c r="B10" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C10" s="10">
         <v>60</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D10" s="10">
         <v>64</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E10" s="10">
         <v>44</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F10" s="10">
         <v>71</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G10" s="10">
         <v>96</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H10" s="10">
         <v>93</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I10" s="10">
         <v>0</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J10" s="10">
         <v>64</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K10" s="10">
         <v>24</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L10" s="10">
         <v>67</v>
       </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B10" s="11" t="s">
+      <c r="P10" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>50</v>
+      </c>
+      <c r="R10" s="10">
+        <v>39</v>
+      </c>
+      <c r="S10" s="10">
+        <v>59</v>
+      </c>
+      <c r="T10" s="10">
+        <v>62</v>
+      </c>
+      <c r="U10" s="10">
+        <v>98</v>
+      </c>
+      <c r="V10" s="10">
+        <v>95</v>
+      </c>
+      <c r="W10" s="10">
+        <v>0</v>
+      </c>
+      <c r="X10" s="10">
+        <v>68</v>
+      </c>
+      <c r="Y10" s="10">
+        <v>10</v>
+      </c>
+      <c r="Z10" s="10">
+        <v>46</v>
+      </c>
+      <c r="AD10" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE10" s="10">
+        <v>71</v>
+      </c>
+      <c r="AF10" s="10">
+        <v>66</v>
+      </c>
+      <c r="AG10" s="10">
+        <v>57</v>
+      </c>
+      <c r="AH10" s="10">
+        <v>77</v>
+      </c>
+      <c r="AI10" s="10">
+        <v>97</v>
+      </c>
+      <c r="AJ10" s="10">
+        <v>92</v>
+      </c>
+      <c r="AK10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="10">
+        <v>68</v>
+      </c>
+      <c r="AM10" s="10">
+        <v>33</v>
+      </c>
+      <c r="AN10" s="10">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="2:40" x14ac:dyDescent="0.35">
+      <c r="B11" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C11" s="10">
         <v>62</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D11" s="10">
         <v>36</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E11" s="10">
         <v>82</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F11" s="10">
         <v>60</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G11" s="10">
         <v>76</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H11" s="10">
         <v>56</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I11" s="10">
         <v>64</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J11" s="10">
         <v>0</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K11" s="10">
         <v>40</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L11" s="10">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B11" s="11" t="s">
+      <c r="P11" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>91</v>
+      </c>
+      <c r="R11" s="10">
+        <v>30</v>
+      </c>
+      <c r="S11" s="10">
+        <v>89</v>
+      </c>
+      <c r="T11" s="10">
+        <v>84</v>
+      </c>
+      <c r="U11" s="10">
+        <v>77</v>
+      </c>
+      <c r="V11" s="10">
+        <v>80</v>
+      </c>
+      <c r="W11" s="10">
+        <v>68</v>
+      </c>
+      <c r="X11" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="10">
+        <v>12</v>
+      </c>
+      <c r="Z11" s="10">
+        <v>32</v>
+      </c>
+      <c r="AD11" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE11" s="10">
+        <v>55</v>
+      </c>
+      <c r="AF11" s="10">
+        <v>24</v>
+      </c>
+      <c r="AG11" s="10">
+        <v>41</v>
+      </c>
+      <c r="AH11" s="10">
+        <v>69</v>
+      </c>
+      <c r="AI11" s="10">
+        <v>84</v>
+      </c>
+      <c r="AJ11" s="10">
+        <v>73</v>
+      </c>
+      <c r="AK11" s="10">
+        <v>68</v>
+      </c>
+      <c r="AL11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="10">
+        <v>20</v>
+      </c>
+      <c r="AN11" s="10">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="2:40" x14ac:dyDescent="0.35">
+      <c r="B12" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C12" s="10">
         <v>49</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D12" s="10">
         <v>22</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E12" s="10">
         <v>53</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F12" s="10">
         <v>47</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G12" s="10">
         <v>42</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H12" s="10">
         <v>31</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I12" s="10">
         <v>24</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J12" s="10">
         <v>40</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K12" s="10">
         <v>0</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L12" s="10">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="11" t="s">
+      <c r="P12" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>48</v>
+      </c>
+      <c r="R12" s="10">
+        <v>1</v>
+      </c>
+      <c r="S12" s="10">
+        <v>26</v>
+      </c>
+      <c r="T12" s="10">
+        <v>19</v>
+      </c>
+      <c r="U12" s="10">
+        <v>17</v>
+      </c>
+      <c r="V12" s="10">
+        <v>14</v>
+      </c>
+      <c r="W12" s="10">
+        <v>10</v>
+      </c>
+      <c r="X12" s="10">
+        <v>12</v>
+      </c>
+      <c r="Y12" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="10">
+        <v>3</v>
+      </c>
+      <c r="AD12" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE12" s="10">
+        <v>22</v>
+      </c>
+      <c r="AF12" s="10">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="10">
+        <v>15</v>
+      </c>
+      <c r="AH12" s="10">
+        <v>27</v>
+      </c>
+      <c r="AI12" s="10">
+        <v>49</v>
+      </c>
+      <c r="AJ12" s="10">
+        <v>39</v>
+      </c>
+      <c r="AK12" s="10">
+        <v>33</v>
+      </c>
+      <c r="AL12" s="10">
+        <v>20</v>
+      </c>
+      <c r="AM12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="10">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="2:40" x14ac:dyDescent="0.35">
+      <c r="B13" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C13" s="10">
         <v>31</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D13" s="10">
         <v>27</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E13" s="10">
         <v>33</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F13" s="10">
         <v>36</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G13" s="10">
         <v>62</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H13" s="10">
         <v>71</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I13" s="10">
         <v>67</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J13" s="10">
         <v>29</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K13" s="10">
         <v>18</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L13" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="2:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="B17" s="20"/>
-      <c r="C17" s="21" t="s">
+      <c r="P13" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>21</v>
+      </c>
+      <c r="R13" s="10">
+        <v>5</v>
+      </c>
+      <c r="S13" s="10">
+        <v>8</v>
+      </c>
+      <c r="T13" s="10">
+        <v>37</v>
+      </c>
+      <c r="U13" s="10">
+        <v>53</v>
+      </c>
+      <c r="V13" s="10">
+        <v>55</v>
+      </c>
+      <c r="W13" s="10">
+        <v>46</v>
+      </c>
+      <c r="X13" s="10">
+        <v>32</v>
+      </c>
+      <c r="Y13" s="10">
+        <v>3</v>
+      </c>
+      <c r="Z13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE13" s="10">
+        <v>47</v>
+      </c>
+      <c r="AF13" s="10">
+        <v>31</v>
+      </c>
+      <c r="AG13" s="10">
+        <v>36</v>
+      </c>
+      <c r="AH13" s="10">
+        <v>53</v>
+      </c>
+      <c r="AI13" s="10">
+        <v>86</v>
+      </c>
+      <c r="AJ13" s="10">
+        <v>81</v>
+      </c>
+      <c r="AK13" s="10">
+        <v>89</v>
+      </c>
+      <c r="AL13" s="10">
+        <v>51</v>
+      </c>
+      <c r="AM13" s="10">
+        <v>26</v>
+      </c>
+      <c r="AN13" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:42" ht="29" x14ac:dyDescent="0.35">
+      <c r="B18" s="16"/>
+      <c r="C18" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D18" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="E18" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="F18" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="G18" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="H17" s="21" t="s">
+      <c r="H18" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="I17" s="21" t="s">
+      <c r="I18" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="J17" s="21" t="s">
+      <c r="J18" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="K17" s="21" t="s">
+      <c r="K18" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="L17" s="21" t="s">
+      <c r="L18" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="M17" s="21" t="s">
+      <c r="M18" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="N17" s="21" t="s">
+      <c r="N18" s="17" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B18" s="11" t="s">
+      <c r="P18" s="16"/>
+      <c r="Q18" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="R18" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="S18" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="T18" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="U18" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="V18" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="W18" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="X18" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y18" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z18" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA18" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB18" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="AD18" s="16"/>
+      <c r="AE18" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="C18" s="10">
+      <c r="AF18" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="AG18" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH18" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="AI18" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="AJ18" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="AK18" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL18" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="AM18" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN18" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO18" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="AP18" s="17" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="19" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="B19" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="C19" s="10">
         <v>0</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D19" s="10">
         <v>96</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E19" s="10">
         <v>92</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F19" s="10">
         <v>85</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G19" s="10">
         <v>81</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H19" s="10">
         <v>77</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I19" s="10">
         <v>65</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J19" s="10">
         <v>58</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K19" s="10">
         <v>42</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L19" s="10">
         <v>40</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M19" s="10">
         <v>31</v>
       </c>
-      <c r="N18" s="10">
+      <c r="N19" s="10">
         <v>35</v>
       </c>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B19" s="11" t="s">
+      <c r="P19" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q19" s="10">
+        <v>0</v>
+      </c>
+      <c r="R19" s="10">
+        <v>72</v>
+      </c>
+      <c r="S19" s="10">
+        <v>78</v>
+      </c>
+      <c r="T19" s="10">
+        <v>70</v>
+      </c>
+      <c r="U19" s="10">
+        <v>85</v>
+      </c>
+      <c r="V19" s="10">
+        <v>80</v>
+      </c>
+      <c r="W19" s="10">
+        <v>55</v>
+      </c>
+      <c r="X19" s="10">
+        <v>40</v>
+      </c>
+      <c r="Y19" s="10">
+        <v>28</v>
+      </c>
+      <c r="Z19" s="10">
+        <v>52</v>
+      </c>
+      <c r="AA19" s="10">
+        <v>45</v>
+      </c>
+      <c r="AB19" s="10">
+        <v>50</v>
+      </c>
+      <c r="AD19" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="AE19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="10">
+        <v>92</v>
+      </c>
+      <c r="AG19" s="10">
+        <v>88</v>
+      </c>
+      <c r="AH19" s="10">
+        <v>95</v>
+      </c>
+      <c r="AI19" s="10">
+        <v>100</v>
+      </c>
+      <c r="AJ19" s="10">
+        <v>90</v>
+      </c>
+      <c r="AK19" s="10">
+        <v>72</v>
+      </c>
+      <c r="AL19" s="10">
+        <v>41</v>
+      </c>
+      <c r="AM19" s="10">
+        <v>33</v>
+      </c>
+      <c r="AN19" s="10">
+        <v>58</v>
+      </c>
+      <c r="AO19" s="10">
+        <v>54</v>
+      </c>
+      <c r="AP19" s="10">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="B20" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C20" s="10">
         <v>96</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D20" s="10">
         <v>0</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E20" s="10">
         <v>89</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F20" s="10">
         <v>83</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G20" s="10">
         <v>78</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H20" s="10">
         <v>75</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I20" s="10">
         <v>60</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J20" s="10">
         <v>63</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K20" s="10">
         <v>38</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L20" s="10">
         <v>51</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M20" s="10">
         <v>33</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N20" s="10">
         <v>29</v>
       </c>
-    </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B20" s="11" t="s">
+      <c r="P20" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q20" s="10">
+        <v>72</v>
+      </c>
+      <c r="R20" s="10">
+        <v>0</v>
+      </c>
+      <c r="S20" s="10">
+        <v>95</v>
+      </c>
+      <c r="T20" s="10">
+        <v>82</v>
+      </c>
+      <c r="U20" s="10">
+        <v>88</v>
+      </c>
+      <c r="V20" s="10">
+        <v>76</v>
+      </c>
+      <c r="W20" s="10">
+        <v>60</v>
+      </c>
+      <c r="X20" s="10">
+        <v>58</v>
+      </c>
+      <c r="Y20" s="10">
+        <v>42</v>
+      </c>
+      <c r="Z20" s="10">
+        <v>56</v>
+      </c>
+      <c r="AA20" s="10">
+        <v>54</v>
+      </c>
+      <c r="AB20" s="10">
+        <v>48</v>
+      </c>
+      <c r="AD20" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="AE20" s="10">
+        <v>92</v>
+      </c>
+      <c r="AF20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="10">
+        <v>94</v>
+      </c>
+      <c r="AH20" s="10">
+        <v>89</v>
+      </c>
+      <c r="AI20" s="10">
+        <v>85</v>
+      </c>
+      <c r="AJ20" s="10">
+        <v>73</v>
+      </c>
+      <c r="AK20" s="10">
+        <v>57</v>
+      </c>
+      <c r="AL20" s="10">
+        <v>68</v>
+      </c>
+      <c r="AM20" s="10">
+        <v>49</v>
+      </c>
+      <c r="AN20" s="10">
+        <v>76</v>
+      </c>
+      <c r="AO20" s="10">
+        <v>46</v>
+      </c>
+      <c r="AP20" s="10">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="B21" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C21" s="10">
         <v>92</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D21" s="10">
         <v>89</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E21" s="10">
         <v>0</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F21" s="10">
         <v>80</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G21" s="10">
         <v>87</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H21" s="10">
         <v>79</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I21" s="10">
         <v>69</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J21" s="10">
         <v>61</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K21" s="10">
         <v>65</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L21" s="10">
         <v>42</v>
       </c>
-      <c r="M20" s="10">
+      <c r="M21" s="10">
         <v>36</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N21" s="10">
         <v>44</v>
       </c>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B21" s="11" t="s">
+      <c r="P21" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q21" s="10">
+        <v>78</v>
+      </c>
+      <c r="R21" s="10">
+        <v>95</v>
+      </c>
+      <c r="S21" s="10">
+        <v>0</v>
+      </c>
+      <c r="T21" s="10">
+        <v>84</v>
+      </c>
+      <c r="U21" s="10">
+        <v>90</v>
+      </c>
+      <c r="V21" s="10">
+        <v>82</v>
+      </c>
+      <c r="W21" s="10">
+        <v>65</v>
+      </c>
+      <c r="X21" s="10">
+        <v>62</v>
+      </c>
+      <c r="Y21" s="10">
+        <v>50</v>
+      </c>
+      <c r="Z21" s="10">
+        <v>48</v>
+      </c>
+      <c r="AA21" s="10">
+        <v>58</v>
+      </c>
+      <c r="AB21" s="10">
+        <v>57</v>
+      </c>
+      <c r="AD21" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE21" s="10">
+        <v>88</v>
+      </c>
+      <c r="AF21" s="10">
+        <v>94</v>
+      </c>
+      <c r="AG21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="10">
+        <v>91</v>
+      </c>
+      <c r="AI21" s="10">
+        <v>87</v>
+      </c>
+      <c r="AJ21" s="10">
+        <v>79</v>
+      </c>
+      <c r="AK21" s="10">
+        <v>63</v>
+      </c>
+      <c r="AL21" s="10">
+        <v>52</v>
+      </c>
+      <c r="AM21" s="10">
+        <v>44</v>
+      </c>
+      <c r="AN21" s="10">
+        <v>71</v>
+      </c>
+      <c r="AO21" s="10">
+        <v>42</v>
+      </c>
+      <c r="AP21" s="10">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="B22" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C22" s="10">
         <v>85</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D22" s="10">
         <v>83</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E22" s="10">
         <v>80</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F22" s="10">
         <v>0</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G22" s="10">
         <v>74</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H22" s="10">
         <v>72</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I22" s="10">
         <v>62</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J22" s="10">
         <v>56</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K22" s="10">
         <v>40</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L22" s="10">
         <v>38</v>
       </c>
-      <c r="M21" s="10">
+      <c r="M22" s="10">
         <v>24</v>
       </c>
-      <c r="N21" s="10">
+      <c r="N22" s="10">
         <v>31</v>
       </c>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B22" s="11" t="s">
+      <c r="P22" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q22" s="10">
+        <v>70</v>
+      </c>
+      <c r="R22" s="10">
+        <v>82</v>
+      </c>
+      <c r="S22" s="10">
+        <v>84</v>
+      </c>
+      <c r="T22" s="10">
+        <v>0</v>
+      </c>
+      <c r="U22" s="10">
+        <v>86</v>
+      </c>
+      <c r="V22" s="10">
+        <v>74</v>
+      </c>
+      <c r="W22" s="10">
+        <v>53</v>
+      </c>
+      <c r="X22" s="10">
+        <v>64</v>
+      </c>
+      <c r="Y22" s="10">
+        <v>46</v>
+      </c>
+      <c r="Z22" s="10">
+        <v>44</v>
+      </c>
+      <c r="AA22" s="10">
+        <v>43</v>
+      </c>
+      <c r="AB22" s="10">
+        <v>41</v>
+      </c>
+      <c r="AD22" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="AE22" s="10">
+        <v>95</v>
+      </c>
+      <c r="AF22" s="10">
+        <v>89</v>
+      </c>
+      <c r="AG22" s="10">
+        <v>91</v>
+      </c>
+      <c r="AH22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="10">
+        <v>96</v>
+      </c>
+      <c r="AJ22" s="10">
+        <v>84</v>
+      </c>
+      <c r="AK22" s="10">
+        <v>66</v>
+      </c>
+      <c r="AL22" s="10">
+        <v>61</v>
+      </c>
+      <c r="AM22" s="10">
+        <v>47</v>
+      </c>
+      <c r="AN22" s="10">
+        <v>74</v>
+      </c>
+      <c r="AO22" s="10">
+        <v>45</v>
+      </c>
+      <c r="AP22" s="10">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="B23" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C23" s="10">
         <v>81</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D23" s="10">
         <v>78</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E23" s="10">
         <v>87</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F23" s="10">
         <v>74</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G23" s="10">
         <v>0</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H23" s="10">
         <v>83</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I23" s="10">
         <v>71</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J23" s="10">
         <v>53</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K23" s="10">
         <v>49</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L23" s="10">
         <v>35</v>
       </c>
-      <c r="M22" s="10">
+      <c r="M23" s="10">
         <v>47</v>
       </c>
-      <c r="N22" s="10">
+      <c r="N23" s="10">
         <v>56</v>
       </c>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B23" s="11" t="s">
+      <c r="P23" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q23" s="10">
+        <v>85</v>
+      </c>
+      <c r="R23" s="10">
+        <v>88</v>
+      </c>
+      <c r="S23" s="10">
+        <v>90</v>
+      </c>
+      <c r="T23" s="10">
+        <v>86</v>
+      </c>
+      <c r="U23" s="10">
+        <v>0</v>
+      </c>
+      <c r="V23" s="10">
+        <v>92</v>
+      </c>
+      <c r="W23" s="10">
+        <v>68</v>
+      </c>
+      <c r="X23" s="10">
+        <v>54</v>
+      </c>
+      <c r="Y23" s="10">
+        <v>38</v>
+      </c>
+      <c r="Z23" s="10">
+        <v>47</v>
+      </c>
+      <c r="AA23" s="10">
+        <v>75</v>
+      </c>
+      <c r="AB23" s="10">
+        <v>66</v>
+      </c>
+      <c r="AD23" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="AE23" s="10">
+        <v>100</v>
+      </c>
+      <c r="AF23" s="10">
+        <v>85</v>
+      </c>
+      <c r="AG23" s="10">
+        <v>87</v>
+      </c>
+      <c r="AH23" s="10">
+        <v>96</v>
+      </c>
+      <c r="AI23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="10">
+        <v>93</v>
+      </c>
+      <c r="AK23" s="10">
+        <v>70</v>
+      </c>
+      <c r="AL23" s="10">
+        <v>43</v>
+      </c>
+      <c r="AM23" s="10">
+        <v>31</v>
+      </c>
+      <c r="AN23" s="10">
+        <v>56</v>
+      </c>
+      <c r="AO23" s="10">
+        <v>51</v>
+      </c>
+      <c r="AP23" s="10">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="B24" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C24" s="10">
         <v>77</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D24" s="10">
         <v>75</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E24" s="10">
         <v>79</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F24" s="10">
         <v>72</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G24" s="10">
         <v>83</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H24" s="10">
         <v>0</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I24" s="10">
         <v>67</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J24" s="10">
         <v>49</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K24" s="10">
         <v>44</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L24" s="10">
         <v>33</v>
       </c>
-      <c r="M23" s="10">
+      <c r="M24" s="10">
         <v>40</v>
       </c>
-      <c r="N23" s="10">
+      <c r="N24" s="10">
         <v>51</v>
       </c>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B24" s="11" t="s">
+      <c r="P24" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q24" s="10">
+        <v>80</v>
+      </c>
+      <c r="R24" s="10">
+        <v>76</v>
+      </c>
+      <c r="S24" s="10">
+        <v>82</v>
+      </c>
+      <c r="T24" s="10">
+        <v>74</v>
+      </c>
+      <c r="U24" s="10">
+        <v>92</v>
+      </c>
+      <c r="V24" s="10">
+        <v>0</v>
+      </c>
+      <c r="W24" s="10">
+        <v>71</v>
+      </c>
+      <c r="X24" s="10">
+        <v>36</v>
+      </c>
+      <c r="Y24" s="10">
+        <v>34</v>
+      </c>
+      <c r="Z24" s="10">
+        <v>39</v>
+      </c>
+      <c r="AA24" s="10">
+        <v>67</v>
+      </c>
+      <c r="AB24" s="10">
+        <v>69</v>
+      </c>
+      <c r="AD24" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="AE24" s="10">
+        <v>90</v>
+      </c>
+      <c r="AF24" s="10">
+        <v>73</v>
+      </c>
+      <c r="AG24" s="10">
+        <v>79</v>
+      </c>
+      <c r="AH24" s="10">
+        <v>84</v>
+      </c>
+      <c r="AI24" s="10">
+        <v>93</v>
+      </c>
+      <c r="AJ24" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="10">
+        <v>65</v>
+      </c>
+      <c r="AL24" s="10">
+        <v>36</v>
+      </c>
+      <c r="AM24" s="10">
+        <v>28</v>
+      </c>
+      <c r="AN24" s="10">
+        <v>48</v>
+      </c>
+      <c r="AO24" s="10">
+        <v>40</v>
+      </c>
+      <c r="AP24" s="10">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="B25" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C25" s="10">
         <v>65</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D25" s="10">
         <v>60</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E25" s="10">
         <v>69</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F25" s="10">
         <v>62</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G25" s="10">
         <v>71</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H25" s="10">
         <v>67</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I25" s="10">
         <v>0</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J25" s="10">
         <v>44</v>
       </c>
-      <c r="K24" s="10">
+      <c r="K25" s="10">
         <v>47</v>
       </c>
-      <c r="L24" s="10">
+      <c r="L25" s="10">
         <v>27</v>
       </c>
-      <c r="M24" s="10">
+      <c r="M25" s="10">
         <v>35</v>
       </c>
-      <c r="N24" s="10">
+      <c r="N25" s="10">
         <v>49</v>
       </c>
-    </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B25" s="11" t="s">
+      <c r="P25" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q25" s="10">
+        <v>55</v>
+      </c>
+      <c r="R25" s="10">
+        <v>60</v>
+      </c>
+      <c r="S25" s="10">
+        <v>65</v>
+      </c>
+      <c r="T25" s="10">
+        <v>53</v>
+      </c>
+      <c r="U25" s="10">
+        <v>68</v>
+      </c>
+      <c r="V25" s="10">
+        <v>71</v>
+      </c>
+      <c r="W25" s="10">
+        <v>0</v>
+      </c>
+      <c r="X25" s="10">
+        <v>25</v>
+      </c>
+      <c r="Y25" s="10">
+        <v>30</v>
+      </c>
+      <c r="Z25" s="10">
+        <v>22</v>
+      </c>
+      <c r="AA25" s="10">
+        <v>49</v>
+      </c>
+      <c r="AB25" s="10">
+        <v>63</v>
+      </c>
+      <c r="AD25" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE25" s="10">
+        <v>72</v>
+      </c>
+      <c r="AF25" s="10">
+        <v>57</v>
+      </c>
+      <c r="AG25" s="10">
+        <v>63</v>
+      </c>
+      <c r="AH25" s="10">
+        <v>66</v>
+      </c>
+      <c r="AI25" s="10">
+        <v>70</v>
+      </c>
+      <c r="AJ25" s="10">
+        <v>65</v>
+      </c>
+      <c r="AK25" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="10">
+        <v>22</v>
+      </c>
+      <c r="AM25" s="10">
+        <v>19</v>
+      </c>
+      <c r="AN25" s="10">
+        <v>34</v>
+      </c>
+      <c r="AO25" s="10">
+        <v>27</v>
+      </c>
+      <c r="AP25" s="10">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="B26" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C26" s="10">
         <v>58</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D26" s="10">
         <v>63</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E26" s="10">
         <v>61</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F26" s="10">
         <v>56</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G26" s="10">
         <v>53</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H26" s="10">
         <v>49</v>
       </c>
-      <c r="I25" s="10">
+      <c r="I26" s="10">
         <v>44</v>
       </c>
-      <c r="J25" s="10">
+      <c r="J26" s="10">
         <v>0</v>
       </c>
-      <c r="K25" s="10">
+      <c r="K26" s="10">
         <v>51</v>
       </c>
-      <c r="L25" s="10">
+      <c r="L26" s="10">
         <v>47</v>
       </c>
-      <c r="M25" s="10">
+      <c r="M26" s="10">
         <v>18</v>
       </c>
-      <c r="N25" s="10">
+      <c r="N26" s="10">
         <v>22</v>
       </c>
-    </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B26" s="11" t="s">
+      <c r="P26" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q26" s="10">
+        <v>40</v>
+      </c>
+      <c r="R26" s="10">
+        <v>58</v>
+      </c>
+      <c r="S26" s="10">
+        <v>62</v>
+      </c>
+      <c r="T26" s="10">
+        <v>64</v>
+      </c>
+      <c r="U26" s="10">
+        <v>54</v>
+      </c>
+      <c r="V26" s="10">
+        <v>36</v>
+      </c>
+      <c r="W26" s="10">
+        <v>25</v>
+      </c>
+      <c r="X26" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="10">
+        <v>26</v>
+      </c>
+      <c r="Z26" s="10">
+        <v>32</v>
+      </c>
+      <c r="AA26" s="10">
+        <v>18</v>
+      </c>
+      <c r="AB26" s="10">
+        <v>20</v>
+      </c>
+      <c r="AD26" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE26" s="10">
+        <v>41</v>
+      </c>
+      <c r="AF26" s="10">
+        <v>68</v>
+      </c>
+      <c r="AG26" s="10">
+        <v>52</v>
+      </c>
+      <c r="AH26" s="10">
+        <v>61</v>
+      </c>
+      <c r="AI26" s="10">
+        <v>43</v>
+      </c>
+      <c r="AJ26" s="10">
+        <v>36</v>
+      </c>
+      <c r="AK26" s="10">
+        <v>22</v>
+      </c>
+      <c r="AL26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="10">
+        <v>17</v>
+      </c>
+      <c r="AN26" s="10">
+        <v>45</v>
+      </c>
+      <c r="AO26" s="10">
+        <v>12</v>
+      </c>
+      <c r="AP26" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="B27" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C27" s="10">
         <v>42</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D27" s="10">
         <v>38</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E27" s="10">
         <v>65</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F27" s="10">
         <v>40</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G27" s="10">
         <v>49</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H27" s="10">
         <v>44</v>
       </c>
-      <c r="I26" s="10">
+      <c r="I27" s="10">
         <v>47</v>
       </c>
-      <c r="J26" s="10">
+      <c r="J27" s="10">
         <v>51</v>
       </c>
-      <c r="K26" s="10">
+      <c r="K27" s="10">
         <v>0</v>
       </c>
-      <c r="L26" s="10">
+      <c r="L27" s="10">
         <v>31</v>
       </c>
-      <c r="M26" s="10">
+      <c r="M27" s="10">
         <v>15</v>
       </c>
-      <c r="N26" s="10">
+      <c r="N27" s="10">
         <v>27</v>
       </c>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B27" s="11" t="s">
+      <c r="P27" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q27" s="10">
+        <v>28</v>
+      </c>
+      <c r="R27" s="10">
+        <v>42</v>
+      </c>
+      <c r="S27" s="10">
+        <v>50</v>
+      </c>
+      <c r="T27" s="10">
+        <v>46</v>
+      </c>
+      <c r="U27" s="10">
+        <v>38</v>
+      </c>
+      <c r="V27" s="10">
+        <v>34</v>
+      </c>
+      <c r="W27" s="10">
+        <v>30</v>
+      </c>
+      <c r="X27" s="10">
+        <v>26</v>
+      </c>
+      <c r="Y27" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="10">
+        <v>15</v>
+      </c>
+      <c r="AA27" s="10">
+        <v>12</v>
+      </c>
+      <c r="AB27" s="10">
+        <v>16</v>
+      </c>
+      <c r="AD27" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE27" s="10">
+        <v>33</v>
+      </c>
+      <c r="AF27" s="10">
+        <v>49</v>
+      </c>
+      <c r="AG27" s="10">
+        <v>44</v>
+      </c>
+      <c r="AH27" s="10">
+        <v>47</v>
+      </c>
+      <c r="AI27" s="10">
+        <v>31</v>
+      </c>
+      <c r="AJ27" s="10">
+        <v>28</v>
+      </c>
+      <c r="AK27" s="10">
+        <v>19</v>
+      </c>
+      <c r="AL27" s="10">
+        <v>17</v>
+      </c>
+      <c r="AM27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="10">
+        <v>29</v>
+      </c>
+      <c r="AO27" s="10">
+        <v>9</v>
+      </c>
+      <c r="AP27" s="10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="B28" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C28" s="10">
         <v>40</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D28" s="10">
         <v>51</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E28" s="10">
         <v>42</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F28" s="10">
         <v>38</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G28" s="10">
         <v>35</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H28" s="10">
         <v>33</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I28" s="10">
         <v>27</v>
       </c>
-      <c r="J27" s="10">
+      <c r="J28" s="10">
         <v>47</v>
       </c>
-      <c r="K27" s="10">
+      <c r="K28" s="10">
         <v>31</v>
       </c>
-      <c r="L27" s="10">
+      <c r="L28" s="10">
         <v>0</v>
       </c>
-      <c r="M27" s="10">
+      <c r="M28" s="10">
         <v>13</v>
       </c>
-      <c r="N27" s="10">
+      <c r="N28" s="10">
         <v>11</v>
       </c>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B28" s="11" t="s">
+      <c r="P28" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q28" s="10">
+        <v>52</v>
+      </c>
+      <c r="R28" s="10">
+        <v>56</v>
+      </c>
+      <c r="S28" s="10">
+        <v>48</v>
+      </c>
+      <c r="T28" s="10">
+        <v>44</v>
+      </c>
+      <c r="U28" s="10">
+        <v>47</v>
+      </c>
+      <c r="V28" s="10">
+        <v>39</v>
+      </c>
+      <c r="W28" s="10">
+        <v>22</v>
+      </c>
+      <c r="X28" s="10">
+        <v>32</v>
+      </c>
+      <c r="Y28" s="10">
+        <v>15</v>
+      </c>
+      <c r="Z28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="10">
+        <v>14</v>
+      </c>
+      <c r="AB28" s="10">
+        <v>10</v>
+      </c>
+      <c r="AD28" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="AE28" s="10">
+        <v>58</v>
+      </c>
+      <c r="AF28" s="10">
+        <v>76</v>
+      </c>
+      <c r="AG28" s="10">
+        <v>71</v>
+      </c>
+      <c r="AH28" s="10">
+        <v>74</v>
+      </c>
+      <c r="AI28" s="10">
+        <v>56</v>
+      </c>
+      <c r="AJ28" s="10">
+        <v>48</v>
+      </c>
+      <c r="AK28" s="10">
+        <v>34</v>
+      </c>
+      <c r="AL28" s="10">
+        <v>45</v>
+      </c>
+      <c r="AM28" s="10">
+        <v>29</v>
+      </c>
+      <c r="AN28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="10">
+        <v>26</v>
+      </c>
+      <c r="AP28" s="10">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="B29" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="C28" s="10">
+      <c r="C29" s="10">
         <v>31</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D29" s="10">
         <v>33</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E29" s="10">
         <v>36</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F29" s="10">
         <v>24</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G29" s="10">
         <v>47</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H29" s="10">
         <v>40</v>
       </c>
-      <c r="I28" s="10">
+      <c r="I29" s="10">
         <v>35</v>
       </c>
-      <c r="J28" s="10">
+      <c r="J29" s="10">
         <v>18</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K29" s="10">
         <v>15</v>
       </c>
-      <c r="L28" s="10">
+      <c r="L29" s="10">
         <v>13</v>
       </c>
-      <c r="M28" s="10">
+      <c r="M29" s="10">
         <v>0</v>
       </c>
-      <c r="N28" s="10">
+      <c r="N29" s="10">
         <v>42</v>
       </c>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B29" s="11" t="s">
+      <c r="P29" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q29" s="10">
+        <v>45</v>
+      </c>
+      <c r="R29" s="10">
+        <v>54</v>
+      </c>
+      <c r="S29" s="10">
+        <v>58</v>
+      </c>
+      <c r="T29" s="10">
+        <v>43</v>
+      </c>
+      <c r="U29" s="10">
+        <v>75</v>
+      </c>
+      <c r="V29" s="10">
+        <v>67</v>
+      </c>
+      <c r="W29" s="10">
+        <v>49</v>
+      </c>
+      <c r="X29" s="10">
+        <v>18</v>
+      </c>
+      <c r="Y29" s="10">
+        <v>12</v>
+      </c>
+      <c r="Z29" s="10">
+        <v>14</v>
+      </c>
+      <c r="AA29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="10">
+        <v>24</v>
+      </c>
+      <c r="AD29" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE29" s="10">
+        <v>54</v>
+      </c>
+      <c r="AF29" s="10">
+        <v>46</v>
+      </c>
+      <c r="AG29" s="10">
+        <v>42</v>
+      </c>
+      <c r="AH29" s="10">
+        <v>45</v>
+      </c>
+      <c r="AI29" s="10">
+        <v>51</v>
+      </c>
+      <c r="AJ29" s="10">
+        <v>40</v>
+      </c>
+      <c r="AK29" s="10">
+        <v>27</v>
+      </c>
+      <c r="AL29" s="10">
+        <v>12</v>
+      </c>
+      <c r="AM29" s="10">
+        <v>9</v>
+      </c>
+      <c r="AN29" s="10">
+        <v>26</v>
+      </c>
+      <c r="AO29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="B30" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C30" s="10">
         <v>35</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D30" s="10">
         <v>29</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E30" s="10">
         <v>44</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F30" s="10">
         <v>31</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G30" s="10">
         <v>56</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H30" s="10">
         <v>51</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I30" s="10">
         <v>49</v>
       </c>
-      <c r="J29" s="10">
+      <c r="J30" s="10">
         <v>22</v>
       </c>
-      <c r="K29" s="10">
+      <c r="K30" s="10">
         <v>27</v>
       </c>
-      <c r="L29" s="10">
+      <c r="L30" s="10">
         <v>11</v>
       </c>
-      <c r="M29" s="10">
+      <c r="M30" s="10">
         <v>42</v>
       </c>
-      <c r="N29" s="10">
+      <c r="N30" s="10">
         <v>0</v>
       </c>
+      <c r="P30" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q30" s="10">
+        <v>50</v>
+      </c>
+      <c r="R30" s="10">
+        <v>48</v>
+      </c>
+      <c r="S30" s="10">
+        <v>57</v>
+      </c>
+      <c r="T30" s="10">
+        <v>41</v>
+      </c>
+      <c r="U30" s="10">
+        <v>66</v>
+      </c>
+      <c r="V30" s="10">
+        <v>69</v>
+      </c>
+      <c r="W30" s="10">
+        <v>63</v>
+      </c>
+      <c r="X30" s="10">
+        <v>20</v>
+      </c>
+      <c r="Y30" s="10">
+        <v>16</v>
+      </c>
+      <c r="Z30" s="10">
+        <v>10</v>
+      </c>
+      <c r="AA30" s="10">
+        <v>24</v>
+      </c>
+      <c r="AB30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="AE30" s="10">
+        <v>61</v>
+      </c>
+      <c r="AF30" s="10">
+        <v>38</v>
+      </c>
+      <c r="AG30" s="10">
+        <v>35</v>
+      </c>
+      <c r="AH30" s="10">
+        <v>39</v>
+      </c>
+      <c r="AI30" s="10">
+        <v>59</v>
+      </c>
+      <c r="AJ30" s="10">
+        <v>67</v>
+      </c>
+      <c r="AK30" s="10">
+        <v>53</v>
+      </c>
+      <c r="AL30" s="10">
+        <v>24</v>
+      </c>
+      <c r="AM30" s="10">
+        <v>21</v>
+      </c>
+      <c r="AN30" s="10">
+        <v>32</v>
+      </c>
+      <c r="AO30" s="10">
+        <v>30</v>
+      </c>
+      <c r="AP30" s="10">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C3:L12">
+  <conditionalFormatting sqref="C4:L13">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C19:N30">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q4:Z13">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q19:AB30">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE4:AN13">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -3995,7 +5801,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:N29">
+  <conditionalFormatting sqref="AE19:AP30">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
